--- a/raw/trend_analysis.xlsx
+++ b/raw/trend_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/cumbung_assessment/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="240" documentId="8_{4CC3F85E-C413-4D2C-B6D6-BE92EA178B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01C5021C-C732-4368-AA41-DF229CD29E7D}"/>
+  <xr:revisionPtr revIDLastSave="242" documentId="8_{4CC3F85E-C413-4D2C-B6D6-BE92EA178B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB912AB-117A-423C-B533-DF6223E7C5E3}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" activeTab="8" xr2:uid="{DAE106E8-A078-4344-BC5B-36A76772C6D7}"/>
+    <workbookView xWindow="768" yWindow="444" windowWidth="19740" windowHeight="13356" firstSheet="1" activeTab="8" xr2:uid="{DAE106E8-A078-4344-BC5B-36A76772C6D7}"/>
   </bookViews>
   <sheets>
     <sheet name="cumbung" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
   <si>
     <t>Year</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Inun_area</t>
-  </si>
-  <si>
-    <t>year</t>
   </si>
   <si>
     <t>Flood</t>
@@ -5566,7 +5563,7 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -6182,16 +6179,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -7486,10 +7483,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>4</v>
-      </c>
-      <c r="B1" t="s">
-        <v>5</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -8054,7 +8051,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -8933,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -9783,16 +9780,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
         <v>6</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -10672,7 +10669,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -11188,7 +11185,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -12470,16 +12467,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
       <c r="D1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">

--- a/raw/trend_analysis.xlsx
+++ b/raw/trend_analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unsw-my.sharepoint.com/personal/z5204897_ad_unsw_edu_au1/Documents/Desktop/Honours_UNSW/Assessment/cumbung_assessment/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="242" documentId="8_{4CC3F85E-C413-4D2C-B6D6-BE92EA178B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB912AB-117A-423C-B533-DF6223E7C5E3}"/>
+  <xr:revisionPtr revIDLastSave="323" documentId="8_{4CC3F85E-C413-4D2C-B6D6-BE92EA178B52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1622836C-F1AD-450B-BB20-D554C0F3B7EF}"/>
   <bookViews>
-    <workbookView xWindow="768" yWindow="444" windowWidth="19740" windowHeight="13356" firstSheet="1" activeTab="8" xr2:uid="{DAE106E8-A078-4344-BC5B-36A76772C6D7}"/>
+    <workbookView xWindow="672" yWindow="1236" windowWidth="22368" windowHeight="13164" xr2:uid="{DAE106E8-A078-4344-BC5B-36A76772C6D7}"/>
   </bookViews>
   <sheets>
     <sheet name="cumbung" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="9">
   <si>
     <t>Year</t>
   </si>
@@ -65,16 +65,10 @@
     <t>Dis_5yr_av</t>
   </si>
   <si>
-    <t>avdischarge</t>
+    <t>Inun_5yr</t>
   </si>
   <si>
-    <t>days&gt;2.175</t>
-  </si>
-  <si>
-    <t>days&gt;3.771</t>
-  </si>
-  <si>
-    <t>Inun_5yr</t>
+    <t>Inun_pred</t>
   </si>
 </sst>
 </file>
@@ -218,99 +212,213 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>cumbung!$E$45:$E$74</c:f>
+              <c:f>cumbung!$F$7:$F$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="68"/>
                 <c:pt idx="0">
-                  <c:v>39.451124999999998</c:v>
+                  <c:v>40.952269764537199</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.494499999999995</c:v>
+                  <c:v>47.232599589128895</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50.793500000000002</c:v>
+                  <c:v>39.05865132830705</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.6785</c:v>
+                  <c:v>48.707826791247655</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.14875</c:v>
+                  <c:v>37.718087674867903</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>24.346625000000003</c:v>
+                  <c:v>36.490310180201327</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>20.365874999999999</c:v>
+                  <c:v>36.893285307957619</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>18.011624999999999</c:v>
+                  <c:v>36.111502905581204</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>18.359500000000001</c:v>
+                  <c:v>24.845397077528482</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>18.356874999999999</c:v>
+                  <c:v>27.915875024197163</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>17.552624999999999</c:v>
+                  <c:v>32.705755281804237</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>16.103000000000002</c:v>
+                  <c:v>30.796579312690341</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.105500000000001</c:v>
+                  <c:v>24.979049020205483</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.5951249999999986</c:v>
+                  <c:v>20.795263227058253</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>5.2641250000000017</c:v>
+                  <c:v>16.056977087992468</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>3.9210000000000003</c:v>
+                  <c:v>9.6314066827137772</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.6432500000000001</c:v>
+                  <c:v>12.901429940149436</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.8927500000000002</c:v>
+                  <c:v>15.836320381201114</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.673875</c:v>
+                  <c:v>16.685907644068298</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>7.1308750000000005</c:v>
+                  <c:v>17.786962952061046</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>14.555000000000001</c:v>
+                  <c:v>20.580887096911447</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>25.182375</c:v>
+                  <c:v>24.757985042129295</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>28.049500000000002</c:v>
+                  <c:v>27.051565474554319</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>29.120625</c:v>
+                  <c:v>32.711455314828697</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>25.77375</c:v>
+                  <c:v>33.836582670907248</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>31.832124999999998</c:v>
+                  <c:v>35.689497787011341</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>24.263375000000003</c:v>
+                  <c:v>24.997509914249783</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>22.202750000000002</c:v>
+                  <c:v>20.726138508756094</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>21.858874999999998</c:v>
+                  <c:v>15.425185569036909</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>21.471249999999998</c:v>
+                  <c:v>13.667233819936772</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5.6559332571680816</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>10.217582626030403</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10.50395827694159</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>11.604749946078631</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.313932731276692</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>13.867501643759841</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>15.13040233936648</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>19.859566556929718</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>20.617250000000002</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>22.211625000000002</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>24.616000000000003</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>19.509875000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>16.046375000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>15.741</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>15.179499999999999</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>17.181374999999999</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>17.382250000000003</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>17.132249999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>16.364625</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>14.942500000000001</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9.3718749999999993</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7.005749999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.0387500000000003</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3.7272500000000002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2.4616250000000002</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.80775</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1.6169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>3.3462499999999999</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>5.9126250000000002</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>10.112500000000001</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.974</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>14.0495</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>13.974</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>16.988500000000002</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>15.574249999999997</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>13.514125000000002</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>13.179374999999999</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>13.332624999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -587,10 +695,10 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>booligal!$D$4:$D$68</c:f>
+              <c:f>booligal!$D$6:$D$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>117.4</c:v>
                 </c:pt>
@@ -603,47 +711,44 @@
                 <c:pt idx="3">
                   <c:v>135.19999999999999</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>108.4</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>68.8</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>80.400000000000006</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>86.8</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>38</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>42.8</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>65</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>68.8</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>50.4</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>43.8</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>37.799999999999997</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>15.4</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>27.6</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>33</c:v>
@@ -652,40 +757,37 @@
                   <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="20">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="21">
                   <c:v>80</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>67.2</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>81</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>81</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>108</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>61</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>46.2</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>17</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>17</c:v>
@@ -694,61 +796,55 @@
                   <c:v>17</c:v>
                 </c:pt>
                 <c:pt idx="34">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="36">
                   <c:v>18.2</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>31.6</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>68.400000000000006</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>70.599999999999994</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>77.8</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>90.6</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>60.2</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>23.4</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>24</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>16.8</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>19.2</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>19.2</c:v>
                 </c:pt>
                 <c:pt idx="46">
                   <c:v>19.2</c:v>
                 </c:pt>
                 <c:pt idx="47">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>19.2</c:v>
+                </c:pt>
+                <c:pt idx="51">
                   <c:v>16.399999999999999</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="52">
                   <c:v>16.399999999999999</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="53">
                   <c:v>0</c:v>
@@ -757,33 +853,45 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="55">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="59">
                   <c:v>3.4</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="60">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="61">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="62">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="63">
                   <c:v>27</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="64">
                   <c:v>49.8</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="65">
                   <c:v>26.2</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="66">
                   <c:v>26.2</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="67">
                   <c:v>26.2</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="68">
                   <c:v>28.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1061,10 +1169,10 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>booligal!$E$4:$E$68</c:f>
+              <c:f>booligal!$E$6:$E$74</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="65"/>
+                <c:ptCount val="69"/>
                 <c:pt idx="0">
                   <c:v>1617.9424895220459</c:v>
                 </c:pt>
@@ -1077,187 +1185,187 @@
                 <c:pt idx="3">
                   <c:v>2079.6602250348087</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="5">
                   <c:v>1790.3489154457675</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
                   <c:v>1394.824161654316</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="7">
                   <c:v>1567.7059052159595</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="8">
                   <c:v>1530.6043342989747</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>947.89371620630266</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="10">
                   <c:v>1079.1935293569873</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="11">
                   <c:v>1295.2375616857546</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="12">
                   <c:v>1204.7194271128083</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
                   <c:v>967.89893775582038</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="14">
                   <c:v>798.08297775582037</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="15">
                   <c:v>606.90728116267769</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="16">
                   <c:v>329.01483759803943</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="17">
                   <c:v>486.85257162304117</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="18">
                   <c:v>595.28557052715075</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="19">
                   <c:v>625.54078312989043</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="20">
                   <c:v>663.76688846470574</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="21">
                   <c:v>1180.0552262759188</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="22">
                   <c:v>1000.9323407964666</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="24">
                   <c:v>1135.6368929979785</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="25">
                   <c:v>1168.6753965596222</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="26">
                   <c:v>1467.6188069960322</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="27">
                   <c:v>965.14906179055322</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="28">
                   <c:v>792.27635204281728</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="29">
                   <c:v>569.86669408788077</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="30">
                   <c:v>504.67358778651089</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="31">
                   <c:v>160.70081189610002</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="32">
                   <c:v>354.32125426304367</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="33">
                   <c:v>364.03100181899845</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="34">
                   <c:v>404.14690318886153</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="35">
                   <c:v>423.96400894228611</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="36">
                   <c:v>494.00626893180623</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="37">
                   <c:v>608.38867040047933</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="38">
                   <c:v>1035.8870616333563</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="39">
                   <c:v>1059.6710473867809</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="40">
                   <c:v>1177.0049683329594</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="41">
                   <c:v>1372.2195505352202</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="42">
                   <c:v>1064.4945965626171</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="43">
                   <c:v>653.80486176809643</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="44">
                   <c:v>670.79782003143941</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="45">
                   <c:v>548.59687607156218</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="46">
                   <c:v>513.94042949621985</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="47">
                   <c:v>524.39686620854877</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="48">
                   <c:v>495.69363552361722</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="51">
                   <c:v>393.21194520547954</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="52">
                   <c:v>356.64857659705075</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="53">
                   <c:v>125.97645440526988</c:v>
                 </c:pt>
-                <c:pt idx="50">
+                <c:pt idx="54">
                   <c:v>75.654822350475314</c:v>
                 </c:pt>
-                <c:pt idx="51">
+                <c:pt idx="55">
                   <c:v>57.487382898420528</c:v>
                 </c:pt>
-                <c:pt idx="52">
+                <c:pt idx="56">
                   <c:v>55.810320211093654</c:v>
                 </c:pt>
-                <c:pt idx="53">
+                <c:pt idx="57">
                   <c:v>53.773728271577212</c:v>
                 </c:pt>
-                <c:pt idx="54">
+                <c:pt idx="58">
                   <c:v>92.966362244179976</c:v>
                 </c:pt>
-                <c:pt idx="55">
+                <c:pt idx="59">
                   <c:v>151.97723703870059</c:v>
                 </c:pt>
-                <c:pt idx="56">
+                <c:pt idx="60">
                   <c:v>419.0803791376602</c:v>
                 </c:pt>
-                <c:pt idx="57">
+                <c:pt idx="61">
                   <c:v>462.58877935923374</c:v>
                 </c:pt>
-                <c:pt idx="58">
+                <c:pt idx="62">
                   <c:v>473.68429387978165</c:v>
                 </c:pt>
-                <c:pt idx="59">
+                <c:pt idx="63">
                   <c:v>465.31725552361729</c:v>
                 </c:pt>
-                <c:pt idx="60">
+                <c:pt idx="64">
                   <c:v>663.73850179953615</c:v>
                 </c:pt>
-                <c:pt idx="61">
+                <c:pt idx="65">
                   <c:v>423.06116353619302</c:v>
                 </c:pt>
-                <c:pt idx="62">
+                <c:pt idx="66">
                   <c:v>387.02859038550804</c:v>
                 </c:pt>
-                <c:pt idx="63">
+                <c:pt idx="67">
                   <c:v>392.70246216633001</c:v>
                 </c:pt>
-                <c:pt idx="64">
+                <c:pt idx="68">
                   <c:v>425.29049792349741</c:v>
                 </c:pt>
               </c:numCache>
@@ -1535,137 +1643,137 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>macquarie!$D$4:$D$46</c:f>
+              <c:f>macquarie!$D$4:$D$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>218</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>220.6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="16">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="17">
                   <c:v>188</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="18">
                   <c:v>186.2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="20">
                   <c:v>153.80000000000001</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="21">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="22">
                   <c:v>62.6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="23">
                   <c:v>51.6</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="24">
                   <c:v>23.6</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="25">
                   <c:v>41</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="26">
                   <c:v>52.8</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="27">
                   <c:v>71.2</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="28">
                   <c:v>79.599999999999994</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="29">
                   <c:v>84.8</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="30">
                   <c:v>99</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="31">
                   <c:v>135.6</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="32">
                   <c:v>123.8</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="33">
                   <c:v>124</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="34">
                   <c:v>140</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="35">
                   <c:v>104.2</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="36">
                   <c:v>58.4</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="37">
                   <c:v>67</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="38">
                   <c:v>60.8</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="39">
                   <c:v>65.2</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="40">
                   <c:v>84.6</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="41">
                   <c:v>139.6</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="42">
                   <c:v>132.19999999999999</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
                   <c:v>134</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="44">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="45">
                   <c:v>76.2</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="46">
                   <c:v>26.8</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="47">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="48">
                   <c:v>10.4</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="49">
                   <c:v>43.4</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="51">
                   <c:v>69.2</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="53">
                   <c:v>110.6</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="54">
                   <c:v>114.6</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="55">
                   <c:v>113.8</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="56">
                   <c:v>80.8</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="57">
                   <c:v>93</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="58">
                   <c:v>60.6</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="59">
                   <c:v>60.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -1943,137 +2051,137 @@
           </c:marker>
           <c:yVal>
             <c:numRef>
-              <c:f>macquarie!$D$4:$D$46</c:f>
+              <c:f>macquarie!$D$4:$D$63</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="43"/>
+                <c:ptCount val="60"/>
                 <c:pt idx="0">
                   <c:v>218</c:v>
                 </c:pt>
-                <c:pt idx="1">
+                <c:pt idx="2">
                   <c:v>220.6</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="16">
                   <c:v>180</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="17">
                   <c:v>188</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="18">
                   <c:v>186.2</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="20">
                   <c:v>153.80000000000001</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="21">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="22">
                   <c:v>62.6</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="23">
                   <c:v>51.6</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="24">
                   <c:v>23.6</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="25">
                   <c:v>41</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="26">
                   <c:v>52.8</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="27">
                   <c:v>71.2</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="28">
                   <c:v>79.599999999999994</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="29">
                   <c:v>84.8</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="30">
                   <c:v>99</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="31">
                   <c:v>135.6</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="32">
                   <c:v>123.8</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="33">
                   <c:v>124</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="34">
                   <c:v>140</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="35">
                   <c:v>104.2</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="36">
                   <c:v>58.4</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="37">
                   <c:v>67</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="38">
                   <c:v>60.8</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="39">
                   <c:v>65.2</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="40">
                   <c:v>84.6</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="41">
                   <c:v>139.6</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="42">
                   <c:v>132.19999999999999</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="43">
                   <c:v>134</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="44">
                   <c:v>100</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="45">
                   <c:v>76.2</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="46">
                   <c:v>26.8</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="47">
                   <c:v>15</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="48">
                   <c:v>10.4</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="49">
                   <c:v>43.4</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="51">
                   <c:v>69.2</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="53">
                   <c:v>110.6</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="54">
                   <c:v>114.6</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="55">
                   <c:v>113.8</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="56">
                   <c:v>80.8</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="57">
                   <c:v>93</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="58">
                   <c:v>60.6</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="59">
                   <c:v>60.2</c:v>
                 </c:pt>
               </c:numCache>
@@ -5056,13 +5164,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>7</xdr:col>
       <xdr:colOff>87630</xdr:colOff>
       <xdr:row>50</xdr:row>
       <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>392430</xdr:colOff>
       <xdr:row>65</xdr:row>
       <xdr:rowOff>26670</xdr:rowOff>
@@ -5097,16 +5205,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>3810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>548640</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>3810</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5133,16 +5241,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>480060</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:rowOff>102870</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>175260</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>110490</xdr:rowOff>
+      <xdr:rowOff>102870</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5174,16 +5282,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>388620</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>3810</xdr:rowOff>
+      <xdr:rowOff>26670</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5210,16 +5318,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>563880</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>281940</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
+      <xdr:colOff>586740</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5546,10 +5654,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DE848C9-6BA0-450E-81A2-BB837B80DAA0}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5557,610 +5665,978 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1946</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2">
+        <v>3.56760949781291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1947</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1948</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1949</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5">
+        <v>15.8309504661704</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1950</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6">
+        <v>68.473365267731594</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>1951</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7">
+        <v>44.305774716363203</v>
+      </c>
+      <c r="F7">
+        <f>AVERAGE(C5:C9)</f>
+        <v>40.952269764537199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>1952</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8">
+        <v>56.450431282737</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ref="F8:F44" si="0">AVERAGE(C6:C10)</f>
+        <v>47.232599589128895</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>1953</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C9">
+        <v>19.700827089683798</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>39.05865132830705</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1954</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>48.707826791247655</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>1955</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C11">
+        <v>35.777572224444199</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>37.718087674867903</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>1956</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C12">
+        <v>82.902476568125607</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>36.490310180201327</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>1957</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C13">
+        <v>12.491474817218</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>36.893285307957619</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>1958</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C14">
+        <v>14.789717111017501</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>36.111502905581204</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>1959</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C15">
+        <v>38.505185818982802</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>24.845397077528482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>1960</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C16">
+        <v>31.868660212562101</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>27.915875024197163</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>1961</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C17">
+        <v>26.571947427862</v>
+      </c>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>32.705755281804237</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>1962</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C18">
+        <v>27.843864550561399</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>30.796579312690341</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>1963</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <v>38.739118399052899</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>24.979049020205483</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>1964</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C20">
+        <v>28.959305973413301</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>20.795263227058253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>1965</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C21">
+        <v>2.7810087501378198</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>16.056977087992468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>1966</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C22">
+        <v>5.6530184621258597</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>9.6314066827137772</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>1967</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C23">
+        <v>4.1524338552324602</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>12.901429940149436</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>1968</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C24">
+        <v>6.6112663726594398</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>15.836320381201114</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>1969</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C25">
+        <v>45.309422260591603</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>16.685907644068298</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>1970</v>
       </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C26">
+        <v>17.455460955396202</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>17.786962952061046</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>1971</v>
       </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C27">
+        <v>9.90095477646177</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>20.580887096911447</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>1972</v>
       </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C28">
+        <v>9.6577103951962098</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>24.757985042129295</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>1973</v>
       </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>27.051565474554319</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>1974</v>
       </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C30">
+        <v>62.017814041462998</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>32.711455314828697</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>1975</v>
       </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="C31">
+        <v>26.629782685096298</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>33.836582670907248</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>1976</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C32">
+        <v>32.540514137559299</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>35.689497787011341</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>1977</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C33">
+        <v>14.1582198195104</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>24.997509914249783</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>1978</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C34">
+        <v>43.101158251427698</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>20.726138508756094</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>1979</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C35">
+        <v>8.5578746776551995</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>15.425185569036909</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>1980</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C36">
+        <v>5.2729256576278702</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>13.667233819936772</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>1981</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C37">
+        <v>6.0357494389633999</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>5.6559332571680816</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>1982</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C38">
+        <v>5.3684610740096899</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>10.217582626030403</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>1983</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C39">
+        <v>3.0446554375842498</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>10.50395827694159</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>1984</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C40">
+        <v>31.3661215219668</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>11.604749946078631</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>1985</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C41">
+        <v>6.7048039121838103</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>12.313932731276692</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>1986</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C42">
+        <v>11.5397077846486</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>13.867501643759841</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>1987</v>
       </c>
       <c r="B43">
-        <v>8.9787499999999998</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+        <v>8.9143749999999997</v>
+      </c>
+      <c r="C43">
+        <v>8.9143749999999997</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>15.13040233936648</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1988</v>
       </c>
       <c r="B44">
-        <v>15.75375</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10.8125</v>
+      </c>
+      <c r="C44">
+        <v>10.8125</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>19.859566556929718</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>1989</v>
       </c>
       <c r="B45">
-        <v>72.928749999999994</v>
-      </c>
-      <c r="E45">
-        <f>AVERAGE(B43:B47)</f>
-        <v>39.451124999999998</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+        <v>37.680624999999999</v>
+      </c>
+      <c r="C45">
+        <v>37.680624999999999</v>
+      </c>
+      <c r="F45">
+        <f>AVERAGE(C43:C47)</f>
+        <v>20.617250000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>1990</v>
       </c>
       <c r="B46">
-        <v>66.412499999999994</v>
-      </c>
-      <c r="E46">
-        <f t="shared" ref="E46:E74" si="0">AVERAGE(B44:B48)</f>
-        <v>44.494499999999995</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+        <v>30.350625000000001</v>
+      </c>
+      <c r="C46">
+        <v>30.350625000000001</v>
+      </c>
+      <c r="F46">
+        <f t="shared" ref="F46:F74" si="1">AVERAGE(C44:C48)</f>
+        <v>22.211625000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>1991</v>
       </c>
       <c r="B47">
-        <v>33.181874999999998</v>
-      </c>
-      <c r="E47">
-        <f t="shared" si="0"/>
-        <v>50.793500000000002</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+        <v>15.328125</v>
+      </c>
+      <c r="C47">
+        <v>15.328125</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="1"/>
+        <v>24.616000000000003</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>1992</v>
       </c>
       <c r="B48">
-        <v>34.195625</v>
-      </c>
-      <c r="E48">
-        <f t="shared" si="0"/>
-        <v>38.6785</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16.88625</v>
+      </c>
+      <c r="C48">
+        <v>16.88625</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>19.509875000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>1993</v>
       </c>
       <c r="B49">
-        <v>47.248750000000001</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="0"/>
-        <v>28.14875</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+        <v>22.834375000000001</v>
+      </c>
+      <c r="C49">
+        <v>22.834375000000001</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>16.046375000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>1994</v>
       </c>
       <c r="B50">
-        <v>12.35375</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="0"/>
-        <v>24.346625000000003</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+        <v>12.15</v>
+      </c>
+      <c r="C50">
+        <v>12.15</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>15.741</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>1995</v>
       </c>
       <c r="B51">
-        <v>13.76375</v>
-      </c>
-      <c r="E51">
-        <f t="shared" si="0"/>
-        <v>20.365874999999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13.033125</v>
+      </c>
+      <c r="C51">
+        <v>13.033125</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>15.179499999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>1996</v>
       </c>
       <c r="B52">
-        <v>14.171250000000001</v>
-      </c>
-      <c r="E52">
-        <f t="shared" si="0"/>
-        <v>18.011624999999999</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13.80125</v>
+      </c>
+      <c r="C52">
+        <v>13.80125</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>17.181374999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>1997</v>
       </c>
       <c r="B53">
-        <v>14.291874999999999</v>
-      </c>
-      <c r="E53">
-        <f t="shared" si="0"/>
-        <v>18.359500000000001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14.078749999999999</v>
+      </c>
+      <c r="C53">
+        <v>14.078749999999999</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>17.382250000000003</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>1998</v>
       </c>
       <c r="B54">
-        <v>35.477499999999999</v>
-      </c>
-      <c r="E54">
-        <f t="shared" si="0"/>
-        <v>18.356874999999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+        <v>32.84375</v>
+      </c>
+      <c r="C54">
+        <v>32.84375</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>17.132249999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>1999</v>
       </c>
       <c r="B55">
-        <v>14.093125000000001</v>
-      </c>
-      <c r="E55">
-        <f t="shared" si="0"/>
-        <v>17.552624999999999</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+        <v>13.154375</v>
+      </c>
+      <c r="C55">
+        <v>13.154375</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>16.364625</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>2000</v>
       </c>
       <c r="B56">
-        <v>13.750624999999999</v>
-      </c>
-      <c r="E56">
-        <f t="shared" si="0"/>
-        <v>16.103000000000002</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+        <v>11.783125</v>
+      </c>
+      <c r="C56">
+        <v>11.783125</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="1"/>
+        <v>14.942500000000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>2001</v>
       </c>
       <c r="B57">
-        <v>10.15</v>
-      </c>
-      <c r="E57">
-        <f t="shared" si="0"/>
-        <v>10.105500000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9.9631249999999998</v>
+      </c>
+      <c r="C57">
+        <v>9.9631249999999998</v>
+      </c>
+      <c r="F57">
+        <f t="shared" si="1"/>
+        <v>9.3718749999999993</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>2002</v>
       </c>
       <c r="B58">
-        <v>7.0437500000000002</v>
-      </c>
-      <c r="E58">
-        <f t="shared" si="0"/>
-        <v>7.5951249999999986</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+        <v>6.9681249999999997</v>
+      </c>
+      <c r="C58">
+        <v>6.9681249999999997</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="1"/>
+        <v>7.005749999999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>2003</v>
       </c>
       <c r="B59">
-        <v>5.49</v>
-      </c>
-      <c r="E59">
-        <f t="shared" si="0"/>
-        <v>5.2641250000000017</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4.9906249999999996</v>
+      </c>
+      <c r="C59">
+        <v>4.9906249999999996</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="1"/>
+        <v>5.0387500000000003</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>2004</v>
       </c>
       <c r="B60">
-        <v>1.54125</v>
-      </c>
-      <c r="E60">
-        <f t="shared" si="0"/>
-        <v>3.9210000000000003</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.32375</v>
+      </c>
+      <c r="C60">
+        <v>1.32375</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="1"/>
+        <v>3.7272500000000002</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>2005</v>
       </c>
       <c r="B61">
-        <v>2.0956250000000001</v>
-      </c>
-      <c r="E61">
-        <f t="shared" si="0"/>
-        <v>2.6432500000000001</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.9481250000000001</v>
+      </c>
+      <c r="C61">
+        <v>1.9481250000000001</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="1"/>
+        <v>2.4616250000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>2006</v>
       </c>
       <c r="B62">
-        <v>3.4343750000000002</v>
-      </c>
-      <c r="E62">
-        <f t="shared" si="0"/>
-        <v>1.8927500000000002</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+        <v>3.4056250000000001</v>
+      </c>
+      <c r="C62">
+        <v>3.4056250000000001</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="1"/>
+        <v>1.80775</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>2007</v>
       </c>
       <c r="B63">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="E63">
-        <f t="shared" si="0"/>
-        <v>1.673875</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.64</v>
+      </c>
+      <c r="C63">
+        <v>0.64</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>1.6169999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>2008</v>
       </c>
       <c r="B64">
-        <v>1.7375</v>
-      </c>
-      <c r="E64">
-        <f t="shared" si="0"/>
-        <v>7.1308750000000005</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+        <v>1.7212499999999999</v>
+      </c>
+      <c r="C64">
+        <v>1.7212499999999999</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>3.3462499999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>2009</v>
       </c>
       <c r="B65">
-        <v>0.44687500000000002</v>
-      </c>
-      <c r="E65">
-        <f t="shared" si="0"/>
-        <v>14.555000000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+        <v>0.37</v>
+      </c>
+      <c r="C65">
+        <v>0.37</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>5.9126250000000002</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>2010</v>
       </c>
       <c r="B66">
-        <v>29.380624999999998</v>
-      </c>
-      <c r="E66">
-        <f t="shared" si="0"/>
-        <v>25.182375</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10.594374999999999</v>
+      </c>
+      <c r="C66">
+        <v>10.594374999999999</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="1"/>
+        <v>10.112500000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>2011</v>
       </c>
       <c r="B67">
-        <v>40.555</v>
-      </c>
-      <c r="E67">
-        <f t="shared" si="0"/>
-        <v>28.049500000000002</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16.237500000000001</v>
+      </c>
+      <c r="C67">
+        <v>16.237500000000001</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="1"/>
+        <v>12.974</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>2012</v>
       </c>
       <c r="B68">
-        <v>53.791874999999997</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="0"/>
-        <v>29.120625</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+        <v>21.639375000000001</v>
+      </c>
+      <c r="C68">
+        <v>21.639375000000001</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>14.0495</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>2013</v>
       </c>
       <c r="B69">
-        <v>16.073125000000001</v>
-      </c>
-      <c r="E69">
-        <f t="shared" si="0"/>
-        <v>25.77375</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16.028749999999999</v>
+      </c>
+      <c r="C69">
+        <v>16.028749999999999</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>13.974</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>2014</v>
       </c>
       <c r="B70">
-        <v>5.8025000000000002</v>
-      </c>
-      <c r="E70">
-        <f t="shared" si="0"/>
-        <v>31.832124999999998</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5.7474999999999996</v>
+      </c>
+      <c r="C70">
+        <v>5.7474999999999996</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="1"/>
+        <v>16.988500000000002</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>2015</v>
       </c>
       <c r="B71">
-        <v>12.64625</v>
-      </c>
-      <c r="E71">
-        <f t="shared" si="0"/>
-        <v>24.263375000000003</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+        <v>10.216875</v>
+      </c>
+      <c r="C71">
+        <v>10.216875</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>15.574249999999997</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>2016</v>
       </c>
       <c r="B72">
-        <v>70.846874999999997</v>
-      </c>
-      <c r="E72">
-        <f t="shared" si="0"/>
-        <v>22.202750000000002</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+        <v>31.31</v>
+      </c>
+      <c r="C72">
+        <v>31.31</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="1"/>
+        <v>13.514125000000002</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>2017</v>
       </c>
       <c r="B73">
-        <v>15.948124999999999</v>
-      </c>
-      <c r="E73">
-        <f t="shared" si="0"/>
-        <v>21.858874999999998</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+        <v>14.568125</v>
+      </c>
+      <c r="C73">
+        <v>14.568125</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="1"/>
+        <v>13.179374999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>2018</v>
       </c>
       <c r="B74">
-        <v>5.77</v>
-      </c>
-      <c r="E74">
-        <f t="shared" si="0"/>
-        <v>21.471249999999998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+        <v>5.7281250000000004</v>
+      </c>
+      <c r="C74">
+        <v>5.7281250000000004</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="1"/>
+        <v>13.332624999999998</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>2019</v>
       </c>
       <c r="B75">
-        <v>4.0831249999999999</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+        <v>4.0737500000000004</v>
+      </c>
+      <c r="C75">
+        <v>4.0737500000000004</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>2020</v>
       </c>
       <c r="B76">
-        <v>10.708125000000001</v>
+        <v>10.983124999999999</v>
+      </c>
+      <c r="C76">
+        <v>10.983124999999999</v>
       </c>
     </row>
   </sheetData>
@@ -6171,7 +6647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{705C0516-F1FD-4A8E-A5D9-D960ED199E85}">
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -6204,1269 +6680,1299 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>1949</v>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>543.05038082191777</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1950</v>
-      </c>
-      <c r="B4">
-        <v>248</v>
-      </c>
-      <c r="C4">
-        <v>3120.9135095890415</v>
-      </c>
-      <c r="D4">
-        <f>AVERAGE(B2:B6)</f>
-        <v>117.4</v>
-      </c>
-      <c r="E4">
-        <f>AVERAGE(C2:C6)</f>
-        <v>1617.9424895220459</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="B5">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>1855.7974849315083</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ref="D5:D36" si="0">AVERAGE(B3:B7)</f>
-        <v>117.4</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E68" si="1">AVERAGE(C3:C7)</f>
-        <v>1740.6322513256987</v>
+        <v>543.05038082191777</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="B6">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="C6">
-        <v>2478.3023306010941</v>
+        <v>3120.9135095890415</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
-        <v>129.4</v>
+        <f>AVERAGE(B2:B8)</f>
+        <v>117.4</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>1919.5583307777536</v>
+        <f>AVERAGE(C2:C8)</f>
+        <v>1617.9424895220459</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="C7">
-        <v>705.09755068493166</v>
+        <v>1855.7974849315083</v>
       </c>
       <c r="D7">
-        <f t="shared" si="0"/>
-        <v>135.19999999999999</v>
+        <f t="shared" ref="D7:D40" si="0">AVERAGE(B5:B9)</f>
+        <v>117.4</v>
       </c>
       <c r="E7">
-        <f t="shared" si="1"/>
-        <v>2079.6602250348087</v>
+        <f t="shared" ref="E7:E74" si="1">AVERAGE(C5:C9)</f>
+        <v>1740.6322513256987</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1955</v>
+        <v>1952</v>
       </c>
       <c r="B8">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="C8">
-        <v>1437.6807780821916</v>
+        <v>2478.3023306010941</v>
       </c>
       <c r="D8">
-        <f t="shared" si="0"/>
-        <v>108.4</v>
+        <f>AVERAGE(B6:B11)</f>
+        <v>129.4</v>
       </c>
       <c r="E8">
-        <f t="shared" si="1"/>
-        <v>1790.3489154457675</v>
+        <f>AVERAGE(C6:C11)</f>
+        <v>1919.5583307777536</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
+        <v>1953</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>705.09755068493166</v>
+      </c>
+      <c r="D9">
+        <f>AVERAGE(B7:B12)</f>
+        <v>135.19999999999999</v>
+      </c>
+      <c r="E9">
+        <f>AVERAGE(C7:C12)</f>
+        <v>2079.6602250348087</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>1955</v>
+      </c>
+      <c r="B11">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>1437.6807780821916</v>
+      </c>
+      <c r="D11">
+        <f>AVERAGE(B8:B13)</f>
+        <v>108.4</v>
+      </c>
+      <c r="E11">
+        <f>AVERAGE(C8:C13)</f>
+        <v>1790.3489154457675</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12">
         <v>1956</v>
       </c>
-      <c r="B9">
+      <c r="B12">
         <v>277</v>
       </c>
-      <c r="C9">
+      <c r="C12">
         <v>3921.4229808743189</v>
       </c>
-      <c r="D9">
+      <c r="D12">
+        <f>AVERAGE(B9:B14)</f>
+        <v>68.8</v>
+      </c>
+      <c r="E12">
+        <f>AVERAGE(C9:C14)</f>
+        <v>1394.824161654316</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1957</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>409.24093698630156</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>80.400000000000006</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>1567.7059052159595</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1958</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>500.67856164383545</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>86.8</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>1530.6043342989747</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1959</v>
+      </c>
+      <c r="B15">
+        <v>58</v>
+      </c>
+      <c r="C15">
+        <v>1569.5062684931499</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>947.89371620630266</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1960</v>
+      </c>
+      <c r="B16">
+        <v>92</v>
+      </c>
+      <c r="C16">
+        <v>1252.1729234972674</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>42.8</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>1079.1935293569873</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1961</v>
+      </c>
+      <c r="B17">
+        <v>33</v>
+      </c>
+      <c r="C17">
+        <v>1007.8698904109589</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>65</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>1295.2375616857546</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1962</v>
+      </c>
+      <c r="B18">
+        <v>30</v>
+      </c>
+      <c r="C18">
+        <v>1065.7400027397246</v>
+      </c>
+      <c r="D18">
         <f t="shared" si="0"/>
         <v>68.8</v>
       </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>1394.824161654316</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>1957</v>
-      </c>
-      <c r="B10">
-        <v>6</v>
-      </c>
-      <c r="C10">
-        <v>409.24093698630156</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>80.400000000000006</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>1567.7059052159595</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>1958</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>500.67856164383545</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>86.8</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>1530.6043342989747</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>1959</v>
-      </c>
-      <c r="B12">
-        <v>58</v>
-      </c>
-      <c r="C12">
-        <v>1569.5062684931499</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="E12">
-        <f t="shared" si="1"/>
-        <v>947.89371620630266</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>1960</v>
-      </c>
-      <c r="B13">
-        <v>92</v>
-      </c>
-      <c r="C13">
-        <v>1252.1729234972674</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>42.8</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="1"/>
-        <v>1079.1935293569873</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>1961</v>
-      </c>
-      <c r="B14">
-        <v>33</v>
-      </c>
-      <c r="C14">
-        <v>1007.8698904109589</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>65</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="1"/>
-        <v>1295.2375616857546</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>1962</v>
-      </c>
-      <c r="B15">
-        <v>30</v>
-      </c>
-      <c r="C15">
-        <v>1065.7400027397246</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>68.8</v>
-      </c>
-      <c r="E15">
+      <c r="E18">
         <f t="shared" si="1"/>
         <v>1204.7194271128083</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
         <v>1963</v>
       </c>
-      <c r="B16">
+      <c r="B19">
         <v>112</v>
       </c>
-      <c r="C16">
+      <c r="C19">
         <v>1580.8987232876721</v>
       </c>
-      <c r="D16">
+      <c r="D19">
         <f t="shared" si="0"/>
         <v>50.4</v>
       </c>
-      <c r="E16">
+      <c r="E19">
         <f t="shared" si="1"/>
         <v>967.89893775582038</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
         <v>1964</v>
       </c>
-      <c r="B17">
+      <c r="B20">
         <v>77</v>
       </c>
-      <c r="C17">
+      <c r="C20">
         <v>1116.9155956284171</v>
       </c>
-      <c r="D17">
+      <c r="D20">
         <f t="shared" si="0"/>
         <v>43.8</v>
       </c>
-      <c r="E17">
+      <c r="E20">
         <f t="shared" si="1"/>
         <v>798.08297775582037</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
         <v>1965</v>
       </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
         <v>68.070476712328798</v>
       </c>
-      <c r="D18">
+      <c r="D21">
         <f t="shared" si="0"/>
         <v>37.799999999999997</v>
       </c>
-      <c r="E18">
+      <c r="E21">
         <f t="shared" si="1"/>
         <v>606.90728116267769</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
         <v>1966</v>
       </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19">
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
         <v>158.79009041095898</v>
       </c>
-      <c r="D19">
+      <c r="D22">
         <f t="shared" si="0"/>
         <v>15.4</v>
       </c>
-      <c r="E19">
+      <c r="E22">
         <f t="shared" si="1"/>
         <v>329.01483759803943</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
         <v>1967</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
         <v>109.86151977401124</v>
       </c>
-      <c r="D20">
+      <c r="D23">
         <f t="shared" si="0"/>
         <v>27.6</v>
       </c>
-      <c r="E20">
+      <c r="E23">
         <f t="shared" si="1"/>
         <v>486.85257162304117</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
         <v>1968</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21">
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
         <v>191.4365054644808</v>
       </c>
-      <c r="D21">
+      <c r="D24">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E21">
+      <c r="E24">
         <f t="shared" si="1"/>
         <v>595.28557052715075</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
         <v>1969</v>
       </c>
-      <c r="B22">
+      <c r="B25">
         <v>138</v>
       </c>
-      <c r="C22">
+      <c r="C25">
         <v>1906.1042657534258</v>
       </c>
-      <c r="D22">
+      <c r="D25">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E22">
+      <c r="E25">
         <f t="shared" si="1"/>
         <v>625.54078312989043</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
         <v>1970</v>
       </c>
-      <c r="B23">
+      <c r="B26">
         <v>27</v>
       </c>
-      <c r="C23">
+      <c r="C26">
         <v>610.23547123287688</v>
       </c>
-      <c r="D23">
+      <c r="D26">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E23">
+      <c r="E26">
         <f t="shared" si="1"/>
         <v>663.76688846470574</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>1971</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>310.06615342465733</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>80</v>
-      </c>
-      <c r="E24">
-        <f t="shared" si="1"/>
-        <v>1180.0552262759188</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>1972</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>300.99204644808719</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>67.2</v>
-      </c>
-      <c r="E25">
-        <f t="shared" si="1"/>
-        <v>1000.9323407964666</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
-        <v>1974</v>
-      </c>
-      <c r="B26">
-        <v>235</v>
-      </c>
-      <c r="C26">
-        <v>2772.8781945205465</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>81</v>
-      </c>
-      <c r="E26">
-        <f t="shared" si="1"/>
-        <v>1135.6368929979785</v>
-      </c>
-    </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="B27">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <v>1010.4898383561651</v>
+        <v>310.06615342465733</v>
       </c>
       <c r="D27">
-        <f t="shared" si="0"/>
-        <v>81</v>
+        <f>AVERAGE(B25:B30)</f>
+        <v>80</v>
       </c>
       <c r="E27">
-        <f t="shared" si="1"/>
-        <v>1168.6753965596222</v>
+        <f>AVERAGE(C25:C30)</f>
+        <v>1180.0552262759188</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
+        <v>1972</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>300.99204644808719</v>
+      </c>
+      <c r="D28">
+        <f>AVERAGE(B26:B31)</f>
+        <v>67.2</v>
+      </c>
+      <c r="E28">
+        <f>AVERAGE(C26:C31)</f>
+        <v>1000.9323407964666</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>1974</v>
+      </c>
+      <c r="B30">
+        <v>235</v>
+      </c>
+      <c r="C30">
+        <v>2772.8781945205465</v>
+      </c>
+      <c r="D30">
+        <f>AVERAGE(B27:B32)</f>
+        <v>81</v>
+      </c>
+      <c r="E30">
+        <f>AVERAGE(C27:C32)</f>
+        <v>1135.6368929979785</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>1975</v>
+      </c>
+      <c r="B31">
+        <v>74</v>
+      </c>
+      <c r="C31">
+        <v>1010.4898383561651</v>
+      </c>
+      <c r="D31">
+        <f>AVERAGE(B28:B33)</f>
+        <v>81</v>
+      </c>
+      <c r="E31">
+        <f>AVERAGE(C28:C33)</f>
+        <v>1168.6753965596222</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>1976</v>
       </c>
-      <c r="B28">
+      <c r="B32">
         <v>96</v>
       </c>
-      <c r="C28">
+      <c r="C32">
         <v>1283.7582322404364</v>
       </c>
-      <c r="D28">
+      <c r="D32">
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="E28">
+      <c r="E32">
         <f t="shared" si="1"/>
         <v>1467.6188069960322</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>1977</v>
       </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29">
+      <c r="B33">
+        <v>0</v>
+      </c>
+      <c r="C33">
         <v>475.25867123287691</v>
       </c>
-      <c r="D29">
+      <c r="D33">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="E29">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>965.14906179055322</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>1978</v>
       </c>
-      <c r="B30">
+      <c r="B34">
         <v>135</v>
       </c>
-      <c r="C30">
+      <c r="C34">
         <v>1795.7090986301364</v>
       </c>
-      <c r="D30">
+      <c r="D34">
         <f t="shared" si="0"/>
         <v>46.2</v>
       </c>
-      <c r="E30">
+      <c r="E34">
         <f t="shared" si="1"/>
         <v>792.27635204281728</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>1979</v>
       </c>
-      <c r="B31">
-        <v>0</v>
-      </c>
-      <c r="C31">
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
         <v>260.5294684931506</v>
       </c>
-      <c r="D31">
+      <c r="D35">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="E31">
+      <c r="E35">
         <f t="shared" si="1"/>
         <v>569.86669408788077</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>1980</v>
       </c>
-      <c r="B32">
-        <v>0</v>
-      </c>
-      <c r="C32">
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
         <v>146.12628961748632</v>
       </c>
-      <c r="D32">
+      <c r="D36">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="E32">
+      <c r="E36">
         <f t="shared" si="1"/>
         <v>504.67358778651089</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>1981</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
         <v>171.70994246575341</v>
       </c>
-      <c r="D33">
+      <c r="D37">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E33">
+      <c r="E37">
         <f t="shared" si="1"/>
         <v>160.70081189610002</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>1982</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38">
         <v>149.2931397260275</v>
       </c>
-      <c r="D34">
+      <c r="D38">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E34">
+      <c r="E38">
         <f t="shared" si="1"/>
         <v>354.32125426304367</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>1983</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
         <v>75.845219178082203</v>
       </c>
-      <c r="D35">
+      <c r="D39">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E35">
+      <c r="E39">
         <f t="shared" si="1"/>
         <v>364.03100181899845</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>1984</v>
       </c>
-      <c r="B36">
+      <c r="B40">
         <v>85</v>
       </c>
-      <c r="C36">
+      <c r="C40">
         <v>1228.6316803278689</v>
       </c>
-      <c r="D36">
+      <c r="D40">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E36">
+      <c r="E40">
         <f t="shared" si="1"/>
         <v>404.14690318886153</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>1985</v>
       </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41">
         <v>194.67502739726035</v>
       </c>
-      <c r="D37">
-        <f t="shared" ref="D37:D68" si="2">AVERAGE(B35:B39)</f>
+      <c r="D41">
+        <f t="shared" ref="D41:D74" si="2">AVERAGE(B39:B43)</f>
         <v>17</v>
       </c>
-      <c r="E37">
+      <c r="E41">
         <f t="shared" si="1"/>
         <v>423.96400894228611</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>1986</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
         <v>372.28944931506868</v>
       </c>
-      <c r="D38">
+      <c r="D42">
         <f t="shared" si="2"/>
         <v>18.2</v>
       </c>
-      <c r="E38">
+      <c r="E42">
         <f t="shared" si="1"/>
         <v>494.00626893180623</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>1987</v>
       </c>
-      <c r="B39">
-        <v>0</v>
-      </c>
-      <c r="C39">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
         <v>248.37866849315051</v>
       </c>
-      <c r="D39">
+      <c r="D43">
         <f t="shared" si="2"/>
         <v>31.6</v>
       </c>
-      <c r="E39">
+      <c r="E43">
         <f t="shared" si="1"/>
         <v>608.38867040047933</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>1988</v>
       </c>
-      <c r="B40">
+      <c r="B44">
         <v>6</v>
       </c>
-      <c r="C40">
+      <c r="C44">
         <v>426.05651912568277</v>
       </c>
-      <c r="D40">
+      <c r="D44">
         <f t="shared" si="2"/>
         <v>68.400000000000006</v>
       </c>
-      <c r="E40">
+      <c r="E44">
         <f t="shared" si="1"/>
         <v>1035.8870616333563</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>1989</v>
       </c>
-      <c r="B41">
+      <c r="B45">
         <v>152</v>
       </c>
-      <c r="C41">
+      <c r="C45">
         <v>1800.5436876712345</v>
       </c>
-      <c r="D41">
+      <c r="D45">
         <f t="shared" si="2"/>
         <v>70.599999999999994</v>
       </c>
-      <c r="E41">
+      <c r="E45">
         <f t="shared" si="1"/>
         <v>1059.6710473867809</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>1990</v>
       </c>
-      <c r="B42">
+      <c r="B46">
         <v>184</v>
       </c>
-      <c r="C42">
+      <c r="C46">
         <v>2332.1669835616444</v>
       </c>
-      <c r="D42">
+      <c r="D46">
         <f t="shared" si="2"/>
         <v>77.8</v>
       </c>
-      <c r="E42">
+      <c r="E46">
         <f t="shared" si="1"/>
         <v>1177.0049683329594</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>1991</v>
       </c>
-      <c r="B43">
+      <c r="B47">
         <v>11</v>
       </c>
-      <c r="C43">
+      <c r="C47">
         <v>491.20937808219179</v>
       </c>
-      <c r="D43">
+      <c r="D47">
         <f t="shared" si="2"/>
         <v>90.6</v>
       </c>
-      <c r="E43">
+      <c r="E47">
         <f t="shared" si="1"/>
         <v>1372.2195505352202</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>1992</v>
       </c>
-      <c r="B44">
+      <c r="B48">
         <v>36</v>
       </c>
-      <c r="C44">
+      <c r="C48">
         <v>835.0482732240439</v>
       </c>
-      <c r="D44">
+      <c r="D48">
         <f t="shared" si="2"/>
         <v>60.2</v>
       </c>
-      <c r="E44">
+      <c r="E48">
         <f t="shared" si="1"/>
         <v>1064.4945965626171</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>1993</v>
       </c>
-      <c r="B45">
+      <c r="B49">
         <v>70</v>
       </c>
-      <c r="C45">
+      <c r="C49">
         <v>1402.1294301369862</v>
       </c>
-      <c r="D45">
+      <c r="D49">
         <f t="shared" si="2"/>
         <v>23.4</v>
       </c>
-      <c r="E45">
+      <c r="E49">
         <f t="shared" si="1"/>
         <v>653.80486176809643</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>1994</v>
       </c>
-      <c r="B46">
-        <v>0</v>
-      </c>
-      <c r="C46">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
         <v>261.91891780821913</v>
       </c>
-      <c r="D46">
+      <c r="D50">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="E46">
+      <c r="E50">
         <f t="shared" si="1"/>
         <v>670.79782003143941</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>1995</v>
       </c>
-      <c r="B47">
-        <v>0</v>
-      </c>
-      <c r="C47">
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
         <v>278.71830958904104</v>
       </c>
-      <c r="D47">
+      <c r="D51">
         <f t="shared" si="2"/>
         <v>16.8</v>
       </c>
-      <c r="E47">
+      <c r="E51">
         <f t="shared" si="1"/>
         <v>548.59687607156218</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>1996</v>
       </c>
-      <c r="B48">
+      <c r="B52">
         <v>14</v>
       </c>
-      <c r="C48">
+      <c r="C52">
         <v>576.174169398907</v>
       </c>
-      <c r="D48">
+      <c r="D52">
         <f t="shared" si="2"/>
         <v>19.2</v>
       </c>
-      <c r="E48">
+      <c r="E52">
         <f t="shared" si="1"/>
         <v>513.94042949621985</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49">
-        <v>1997</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49">
-        <v>224.04355342465752</v>
-      </c>
-      <c r="D49">
-        <f t="shared" si="2"/>
-        <v>19.2</v>
-      </c>
-      <c r="E49">
-        <f t="shared" si="1"/>
-        <v>524.39686620854877</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50">
-        <v>1998</v>
-      </c>
-      <c r="B50">
-        <v>82</v>
-      </c>
-      <c r="C50">
-        <v>1228.8471972602745</v>
-      </c>
-      <c r="D50">
-        <f t="shared" si="2"/>
-        <v>19.2</v>
-      </c>
-      <c r="E50">
-        <f t="shared" si="1"/>
-        <v>495.69363552361722</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51">
-        <v>2001</v>
-      </c>
-      <c r="B51">
-        <v>0</v>
-      </c>
-      <c r="C51">
-        <v>314.20110136986324</v>
-      </c>
-      <c r="D51">
-        <f t="shared" si="2"/>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E51">
-        <f t="shared" si="1"/>
-        <v>393.21194520547954</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>2002</v>
-      </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>135.20215616438355</v>
-      </c>
-      <c r="D52">
-        <f t="shared" si="2"/>
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E52">
-        <f t="shared" si="1"/>
-        <v>356.64857659705075</v>
-      </c>
-    </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53">
+        <v>1997</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>224.04355342465752</v>
+      </c>
+      <c r="D53">
+        <f>AVERAGE(B51:B57)</f>
+        <v>19.2</v>
+      </c>
+      <c r="E53">
+        <f>AVERAGE(C51:C57)</f>
+        <v>524.39686620854877</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1998</v>
+      </c>
+      <c r="B54">
+        <v>82</v>
+      </c>
+      <c r="C54">
+        <v>1228.8471972602745</v>
+      </c>
+      <c r="D54">
+        <f>AVERAGE(B52:B58)</f>
+        <v>19.2</v>
+      </c>
+      <c r="E54">
+        <f>AVERAGE(C52:C58)</f>
+        <v>495.69363552361722</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>2001</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>314.20110136986324</v>
+      </c>
+      <c r="D57">
+        <f>AVERAGE(B53:B59)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E57">
+        <f>AVERAGE(C53:C59)</f>
+        <v>393.21194520547954</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>2002</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>135.20215616438355</v>
+      </c>
+      <c r="D58">
+        <f>AVERAGE(B54:B60)</f>
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E58">
+        <f>AVERAGE(C54:C60)</f>
+        <v>356.64857659705075</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>2003</v>
       </c>
-      <c r="B53">
-        <v>0</v>
-      </c>
-      <c r="C53">
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
         <v>63.765717808219129</v>
       </c>
-      <c r="D53">
+      <c r="D59">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E53">
+      <c r="E59">
         <f t="shared" si="1"/>
         <v>125.97645440526988</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>2004</v>
       </c>
-      <c r="B54">
-        <v>0</v>
-      </c>
-      <c r="C54">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
         <v>41.226710382513652</v>
       </c>
-      <c r="D54">
+      <c r="D60">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E54">
+      <c r="E60">
         <f t="shared" si="1"/>
         <v>75.654822350475314</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>2005</v>
       </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
         <v>75.486586301369854</v>
       </c>
-      <c r="D55">
+      <c r="D61">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E55">
+      <c r="E61">
         <f t="shared" si="1"/>
         <v>57.487382898420528</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>2006</v>
       </c>
-      <c r="B56">
-        <v>0</v>
-      </c>
-      <c r="C56">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>62.592941095890431</v>
       </c>
-      <c r="D56">
+      <c r="D62">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E56">
+      <c r="E62">
         <f t="shared" si="1"/>
         <v>55.810320211093654</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>2007</v>
       </c>
-      <c r="B57">
-        <v>0</v>
-      </c>
-      <c r="C57">
+      <c r="B63">
+        <v>0</v>
+      </c>
+      <c r="C63">
         <v>44.364958904109578</v>
       </c>
-      <c r="D57">
+      <c r="D63">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E57">
+      <c r="E63">
         <f t="shared" si="1"/>
         <v>53.773728271577212</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64">
         <v>2008</v>
       </c>
-      <c r="B58">
-        <v>0</v>
-      </c>
-      <c r="C58">
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
         <v>55.380404371584717</v>
       </c>
-      <c r="D58">
+      <c r="D64">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="E58">
+      <c r="E64">
         <f t="shared" si="1"/>
         <v>92.966362244179976</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>2009</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59">
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
         <v>31.04375068493151</v>
       </c>
-      <c r="D59">
+      <c r="D65">
         <f t="shared" si="2"/>
         <v>3.4</v>
       </c>
-      <c r="E59">
+      <c r="E65">
         <f t="shared" si="1"/>
         <v>151.97723703870059</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66">
         <v>2010</v>
       </c>
-      <c r="B60">
-        <v>0</v>
-      </c>
-      <c r="C60">
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
         <v>271.44975616438359</v>
       </c>
-      <c r="D60">
+      <c r="D66">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="E60">
+      <c r="E66">
         <f t="shared" si="1"/>
         <v>419.0803791376602</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67">
         <v>2011</v>
       </c>
-      <c r="B61">
+      <c r="B67">
         <v>17</v>
       </c>
-      <c r="C61">
+      <c r="C67">
         <v>357.6473150684937</v>
       </c>
-      <c r="D61">
+      <c r="D67">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="E61">
+      <c r="E67">
         <f t="shared" si="1"/>
         <v>462.58877935923374</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68">
         <v>2012</v>
       </c>
-      <c r="B62">
+      <c r="B68">
         <v>118</v>
       </c>
-      <c r="C62">
+      <c r="C68">
         <v>1379.8806693989077</v>
       </c>
-      <c r="D62">
+      <c r="D68">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="E62">
+      <c r="E68">
         <f t="shared" si="1"/>
         <v>473.68429387978165</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69">
         <v>2013</v>
       </c>
-      <c r="B63">
-        <v>0</v>
-      </c>
-      <c r="C63">
+      <c r="B69">
+        <v>0</v>
+      </c>
+      <c r="C69">
         <v>272.92240547945227</v>
       </c>
-      <c r="D63">
+      <c r="D69">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="E63">
+      <c r="E69">
         <f t="shared" si="1"/>
         <v>465.31725552361729</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70">
         <v>2014</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64">
+      <c r="B70">
+        <v>0</v>
+      </c>
+      <c r="C70">
         <v>86.521323287671251</v>
       </c>
-      <c r="D64">
+      <c r="D70">
         <f t="shared" si="2"/>
         <v>49.8</v>
       </c>
-      <c r="E64">
+      <c r="E70">
         <f t="shared" si="1"/>
         <v>663.73850179953615</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71">
         <v>2015</v>
       </c>
-      <c r="B65">
-        <v>0</v>
-      </c>
-      <c r="C65">
+      <c r="B71">
+        <v>0</v>
+      </c>
+      <c r="C71">
         <v>229.61456438356171</v>
       </c>
-      <c r="D65">
+      <c r="D71">
         <f t="shared" si="2"/>
         <v>26.2</v>
       </c>
-      <c r="E65">
+      <c r="E71">
         <f t="shared" si="1"/>
         <v>423.06116353619302</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72">
         <v>2016</v>
       </c>
-      <c r="B66">
+      <c r="B72">
         <v>131</v>
       </c>
-      <c r="C66">
+      <c r="C72">
         <v>1349.7535464480879</v>
       </c>
-      <c r="D66">
+      <c r="D72">
         <f t="shared" si="2"/>
         <v>26.2</v>
       </c>
-      <c r="E66">
+      <c r="E72">
         <f t="shared" si="1"/>
         <v>387.02859038550804</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73">
         <v>2017</v>
       </c>
-      <c r="B67">
-        <v>0</v>
-      </c>
-      <c r="C67">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
         <v>176.4939780821918</v>
       </c>
-      <c r="D67">
+      <c r="D73">
         <f t="shared" si="2"/>
         <v>26.2</v>
       </c>
-      <c r="E67">
+      <c r="E73">
         <f t="shared" si="1"/>
         <v>392.70246216633001</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74">
         <v>2018</v>
       </c>
-      <c r="B68">
-        <v>0</v>
-      </c>
-      <c r="C68">
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
         <v>92.759539726027427</v>
       </c>
-      <c r="D68">
+      <c r="D74">
         <f t="shared" si="2"/>
         <v>28.4</v>
       </c>
-      <c r="E68">
+      <c r="E74">
         <f t="shared" si="1"/>
         <v>425.29049792349741</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75">
         <v>2019</v>
       </c>
-      <c r="B69">
-        <v>0</v>
-      </c>
-      <c r="C69">
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
         <v>114.89068219178093</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76">
         <v>2020</v>
       </c>
-      <c r="B70">
+      <c r="B76">
         <v>11</v>
       </c>
-      <c r="C70">
+      <c r="C76">
         <v>392.55474316939899</v>
       </c>
     </row>
@@ -7478,7 +7984,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1B8F64-BBC5-4E39-B655-C5A5E3668C7F}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -7513,526 +8019,731 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>1971</v>
-      </c>
-      <c r="B4">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>5866.5352054794494</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1972</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>371.44581147540981</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1973</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
-      </c>
-      <c r="C6">
-        <v>1518.9892821917792</v>
+        <v>1934</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1974</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>1130.9892821917849</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1977</v>
-      </c>
-      <c r="B8">
-        <v>9</v>
-      </c>
-      <c r="C8">
-        <v>2353.0994191780815</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1978</v>
-      </c>
-      <c r="B9">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>2135.5402904109587</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1979</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>328.5161780821918</v>
+        <v>1938</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1980</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>301.07724590163917</v>
+        <v>1939</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>1981</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>306.12934794520561</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>1982</v>
-      </c>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>515.8056136986304</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>1983</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>1246.3005232876721</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>1984</v>
-      </c>
-      <c r="C15">
-        <v>2605.0263469945357</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>1985</v>
-      </c>
-      <c r="B16">
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>484.68242465753417</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>1986</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>316.48114794520552</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>1987</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18">
-        <v>238.96343287671215</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1946</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>1988</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>551.83717759562762</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>1989</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>307.61333150684931</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1948</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>1990</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>433.26006301369819</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1949</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>1991</v>
-      </c>
-      <c r="B22">
-        <v>2</v>
-      </c>
-      <c r="C22">
-        <v>506.64393424657572</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>1992</v>
-      </c>
-      <c r="B23">
-        <v>0</v>
-      </c>
-      <c r="C23">
-        <v>183.20473224043721</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>1993</v>
-      </c>
-      <c r="B24">
-        <v>0</v>
-      </c>
-      <c r="C24">
-        <v>90.17517260273975</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1952</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>1994</v>
-      </c>
-      <c r="B25">
-        <v>0</v>
-      </c>
-      <c r="C25">
-        <v>81.627265753424638</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>1995</v>
-      </c>
-      <c r="B26">
-        <v>5</v>
-      </c>
-      <c r="C26">
-        <v>553.50873424657527</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1954</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>1996</v>
-      </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27">
-        <v>922.59617213114655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>1997</v>
-      </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-      <c r="C28">
-        <v>999.3949863013703</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1956</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>1998</v>
-      </c>
-      <c r="B29">
-        <v>16</v>
-      </c>
-      <c r="C29">
-        <v>2653.283687671234</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>1999</v>
-      </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-      <c r="C30">
-        <v>550.26475068493176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1958</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>2000</v>
-      </c>
-      <c r="B31">
-        <v>8</v>
-      </c>
-      <c r="C31">
-        <v>1126.0095191256835</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>2001</v>
-      </c>
-      <c r="B32">
-        <v>7</v>
-      </c>
-      <c r="C32">
-        <v>1104.6090958904099</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>2002</v>
-      </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-      <c r="C33">
-        <v>302.81320821917842</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>2003</v>
-      </c>
-      <c r="B34">
-        <v>2</v>
-      </c>
-      <c r="C34">
-        <v>455.27861917808275</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>2004</v>
-      </c>
-      <c r="B35">
-        <v>7</v>
-      </c>
-      <c r="C35">
-        <v>1077.5301994535512</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>2005</v>
-      </c>
-      <c r="B36">
-        <v>2</v>
-      </c>
-      <c r="C36">
-        <v>408.82022465753414</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>2006</v>
-      </c>
-      <c r="B37">
-        <v>0</v>
-      </c>
-      <c r="C37">
-        <v>216.93927397260288</v>
+        <v>1965</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>2007</v>
-      </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
-        <v>178.39026301369847</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>2008</v>
-      </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-      <c r="C39">
-        <v>279.44896994535509</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>2009</v>
-      </c>
-      <c r="B40">
-        <v>0</v>
-      </c>
-      <c r="C40">
-        <v>189.19329041095881</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>2010</v>
-      </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41">
-        <v>523.79046027397283</v>
+        <v>1969</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>2011</v>
-      </c>
-      <c r="B42">
-        <v>11</v>
-      </c>
-      <c r="C42">
-        <v>1655.0705589041097</v>
+        <v>1970</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>2012</v>
+        <v>1971</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="C43">
-        <v>1750.288396174861</v>
+        <v>5866.5352054794494</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>2013</v>
+        <v>1972</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>635.59680547945186</v>
+        <v>371.44581147540981</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>2014</v>
+        <v>1973</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C45">
-        <v>295.49839178082175</v>
+        <v>1518.9892821917792</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>2015</v>
+        <v>1974</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>292.14737260273949</v>
+        <v>1130.9892821917849</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>2016</v>
-      </c>
-      <c r="B47">
-        <v>4</v>
-      </c>
-      <c r="C47">
-        <v>641.02806010928941</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>2017</v>
-      </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-      <c r="C48">
-        <v>348.6916904109587</v>
+        <v>1976</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>2018</v>
+        <v>1977</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C49">
-        <v>255.42000821917813</v>
+        <v>2353.0994191780815</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>2019</v>
+        <v>1978</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C50">
-        <v>65.842375342465701</v>
+        <v>2135.5402904109587</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51">
+        <v>1979</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>328.5161780821918</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>1980</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>301.07724590163917</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>1981</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>306.12934794520561</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>1982</v>
+      </c>
+      <c r="B54">
+        <v>3</v>
+      </c>
+      <c r="C54">
+        <v>515.8056136986304</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>1983</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+      <c r="C55">
+        <v>1246.3005232876721</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>1984</v>
+      </c>
+      <c r="C56">
+        <v>2605.0263469945357</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>1985</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+      <c r="C57">
+        <v>484.68242465753417</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>1986</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>316.48114794520552</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>1987</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>238.96343287671215</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>1988</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>551.83717759562762</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>1989</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>307.61333150684931</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>1990</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>433.26006301369819</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>1991</v>
+      </c>
+      <c r="B63">
+        <v>2</v>
+      </c>
+      <c r="C63">
+        <v>506.64393424657572</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>1992</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64">
+        <v>183.20473224043721</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1993</v>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+      <c r="C65">
+        <v>90.17517260273975</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>1994</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>81.627265753424638</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>1995</v>
+      </c>
+      <c r="B67">
+        <v>5</v>
+      </c>
+      <c r="C67">
+        <v>553.50873424657527</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>1996</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>922.59617213114655</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>1997</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
+      </c>
+      <c r="C69">
+        <v>999.3949863013703</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>1998</v>
+      </c>
+      <c r="B70">
+        <v>16</v>
+      </c>
+      <c r="C70">
+        <v>2653.283687671234</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>1999</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>550.26475068493176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>2000</v>
+      </c>
+      <c r="B72">
+        <v>8</v>
+      </c>
+      <c r="C72">
+        <v>1126.0095191256835</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>2001</v>
+      </c>
+      <c r="B73">
+        <v>7</v>
+      </c>
+      <c r="C73">
+        <v>1104.6090958904099</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>2002</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>302.81320821917842</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>2003</v>
+      </c>
+      <c r="B75">
+        <v>2</v>
+      </c>
+      <c r="C75">
+        <v>455.27861917808275</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>2004</v>
+      </c>
+      <c r="B76">
+        <v>7</v>
+      </c>
+      <c r="C76">
+        <v>1077.5301994535512</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>2005</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>408.82022465753414</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>2006</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>216.93927397260288</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>2007</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>178.39026301369847</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>2008</v>
+      </c>
+      <c r="B80">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>279.44896994535509</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>2009</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>189.19329041095881</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>2010</v>
+      </c>
+      <c r="B82">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>523.79046027397283</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>2011</v>
+      </c>
+      <c r="B83">
+        <v>11</v>
+      </c>
+      <c r="C83">
+        <v>1655.0705589041097</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>2012</v>
+      </c>
+      <c r="B84">
+        <v>9</v>
+      </c>
+      <c r="C84">
+        <v>1750.288396174861</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>2013</v>
+      </c>
+      <c r="B85">
+        <v>4</v>
+      </c>
+      <c r="C85">
+        <v>635.59680547945186</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>2014</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>295.49839178082175</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>2015</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>292.14737260273949</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>2016</v>
+      </c>
+      <c r="B88">
+        <v>4</v>
+      </c>
+      <c r="C88">
+        <v>641.02806010928941</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>2017</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>348.6916904109587</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>2018</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>255.42000821917813</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>2019</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>65.842375342465701</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A92">
         <v>2020</v>
       </c>
-      <c r="B51">
+      <c r="B92">
         <v>1</v>
       </c>
-      <c r="C51">
+      <c r="C92">
         <v>286.69618032786877</v>
       </c>
     </row>
@@ -8922,7 +9633,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87DF4C78-37B1-4908-96BE-A01D3AFE7CF3}">
-  <dimension ref="A1:C93"/>
+  <dimension ref="A1:C107"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -9613,155 +10324,267 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A80">
-        <v>2007</v>
-      </c>
-      <c r="B80">
-        <v>0</v>
+        <v>1993</v>
       </c>
       <c r="C80">
-        <v>409.74072876712347</v>
+        <v>5127.6103443993798</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
-        <v>2008</v>
-      </c>
-      <c r="B81">
-        <v>0</v>
+        <v>1994</v>
       </c>
       <c r="C81">
-        <v>581.43102185792327</v>
+        <v>954.92618424879504</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
-        <v>2009</v>
-      </c>
-      <c r="B82">
-        <v>0</v>
+        <v>1995</v>
       </c>
       <c r="C82">
-        <v>561.99222191780802</v>
+        <v>2431.9671019389202</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
-        <v>2010</v>
-      </c>
-      <c r="B83">
-        <v>62</v>
+        <v>1996</v>
       </c>
       <c r="C83">
-        <v>2474.3580164383561</v>
+        <v>3000.14431056789</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
-        <v>2011</v>
-      </c>
-      <c r="B84">
-        <v>46</v>
+        <v>1997</v>
       </c>
       <c r="C84">
-        <v>4520.5243917808211</v>
+        <v>946.75444391974804</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
-        <v>2012</v>
-      </c>
-      <c r="B85">
-        <v>107</v>
+        <v>1998</v>
       </c>
       <c r="C85">
-        <v>5952.4328442622964</v>
+        <v>1822.5440034784101</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
-        <v>2013</v>
-      </c>
-      <c r="B86">
-        <v>0</v>
+        <v>1999</v>
       </c>
       <c r="C86">
-        <v>1056.8171643835608</v>
+        <v>1242.70333811091</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
-        <v>2014</v>
-      </c>
-      <c r="B87">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="C87">
-        <v>1192.2818931506843</v>
+        <v>2174.8488595026702</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
-        <v>2015</v>
-      </c>
-      <c r="B88">
-        <v>0</v>
+        <v>2001</v>
       </c>
       <c r="C88">
-        <v>1600.0128493150678</v>
+        <v>1157.87611994079</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
-        <v>2016</v>
-      </c>
-      <c r="B89">
-        <v>101</v>
+        <v>2002</v>
       </c>
       <c r="C89">
-        <v>5105.3591803278669</v>
+        <v>756.89829495577101</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
-        <v>2017</v>
-      </c>
-      <c r="B90">
-        <v>3</v>
+        <v>2003</v>
       </c>
       <c r="C90">
-        <v>1798.9819095890414</v>
+        <v>748.71958226233698</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
-        <v>2018</v>
-      </c>
-      <c r="B91">
-        <v>0</v>
+        <v>2004</v>
       </c>
       <c r="C91">
-        <v>753.34994794520583</v>
+        <v>618.76278656264003</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
-        <v>2019</v>
-      </c>
-      <c r="B92">
-        <v>0</v>
+        <v>2005</v>
       </c>
       <c r="C92">
-        <v>1004.9312958904114</v>
+        <v>896.88040535378104</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
+        <v>2006</v>
+      </c>
+      <c r="C93">
+        <v>607.55767949505196</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>2007</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>409.74072876712347</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>2008</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>581.43102185792327</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>2009</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>561.99222191780802</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>2010</v>
+      </c>
+      <c r="B97">
+        <v>62</v>
+      </c>
+      <c r="C97">
+        <v>2474.3580164383561</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>2011</v>
+      </c>
+      <c r="B98">
+        <v>46</v>
+      </c>
+      <c r="C98">
+        <v>4520.5243917808211</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>2012</v>
+      </c>
+      <c r="B99">
+        <v>107</v>
+      </c>
+      <c r="C99">
+        <v>5952.4328442622964</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>2013</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1056.8171643835608</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>2014</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>1192.2818931506843</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>2015</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1600.0128493150678</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>2016</v>
+      </c>
+      <c r="B103">
+        <v>101</v>
+      </c>
+      <c r="C103">
+        <v>5105.3591803278669</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>2017</v>
+      </c>
+      <c r="B104">
+        <v>3</v>
+      </c>
+      <c r="C104">
+        <v>1798.9819095890414</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>2018</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>753.34994794520583</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>2019</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>1004.9312958904114</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A107">
         <v>2020</v>
       </c>
-      <c r="B93">
-        <v>0</v>
-      </c>
-      <c r="C93">
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
         <v>1324.2107158469939</v>
       </c>
     </row>
@@ -9772,7 +10595,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDC8953-FB9D-495C-A475-A454FE739CCA}">
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
@@ -9825,831 +10648,916 @@
         <v>557.11288219178095</v>
       </c>
       <c r="D4">
-        <f>AVERAGE(B2:B6)</f>
+        <f>AVERAGE(B2:B20)</f>
         <v>218</v>
       </c>
       <c r="E4">
-        <f>AVERAGE(C2:C6)</f>
+        <f>AVERAGE(C2:C20)</f>
         <v>2105.7845802036077</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>1959</v>
-      </c>
-      <c r="B5">
-        <v>191</v>
-      </c>
-      <c r="C5">
-        <v>2134.828410958904</v>
-      </c>
-      <c r="D5">
-        <f t="shared" ref="D5:D45" si="0">AVERAGE(B3:B7)</f>
-        <v>220.6</v>
-      </c>
-      <c r="E5">
-        <f t="shared" ref="E5:E46" si="1">AVERAGE(C3:C7)</f>
-        <v>2094.3692739022367</v>
+        <v>1958</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>1973</v>
+        <v>1959</v>
       </c>
       <c r="B6">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="C6">
-        <v>2140.4230273972612</v>
+        <v>2134.828410958904</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
-        <v>180</v>
+        <f>AVERAGE(B3:B21)</f>
+        <v>220.6</v>
       </c>
       <c r="E6">
-        <f t="shared" si="1"/>
-        <v>1625.3425457534245</v>
+        <f>AVERAGE(C3:C21)</f>
+        <v>2094.3692739022367</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>1974</v>
-      </c>
-      <c r="B7">
-        <v>326</v>
-      </c>
-      <c r="C7">
-        <v>2287.9429205479451</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>188</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="1"/>
-        <v>1656.1655090410957</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>1975</v>
-      </c>
-      <c r="B8">
-        <v>157</v>
-      </c>
-      <c r="C8">
-        <v>1006.4054876712324</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>186.2</v>
-      </c>
-      <c r="E8">
-        <f t="shared" si="1"/>
-        <v>1510.6220635616437</v>
+        <v>1961</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>1977</v>
-      </c>
-      <c r="B9">
-        <v>61</v>
-      </c>
-      <c r="C9">
-        <v>711.22769863013707</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>153.80000000000001</v>
-      </c>
-      <c r="E9">
-        <f t="shared" si="1"/>
-        <v>1207.6503063013695</v>
+        <v>1962</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>1978</v>
-      </c>
-      <c r="B10">
-        <v>182</v>
-      </c>
-      <c r="C10">
-        <v>1407.1111835616432</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>90</v>
-      </c>
-      <c r="E10">
-        <f t="shared" si="1"/>
-        <v>818.86477519724508</v>
+        <v>1963</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>1979</v>
-      </c>
-      <c r="B11">
-        <v>43</v>
-      </c>
-      <c r="C11">
-        <v>625.56424109589022</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>62.6</v>
-      </c>
-      <c r="E11">
-        <f t="shared" si="1"/>
-        <v>666.04050423834099</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12">
+        <v>1965</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>1972</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>1973</v>
+      </c>
+      <c r="B20">
+        <v>205</v>
+      </c>
+      <c r="C20">
+        <v>2140.4230273972612</v>
+      </c>
+      <c r="D20">
+        <f>AVERAGE(B4:B22)</f>
+        <v>180</v>
+      </c>
+      <c r="E20">
+        <f>AVERAGE(C4:C22)</f>
+        <v>1625.3425457534245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>1974</v>
+      </c>
+      <c r="B21">
+        <v>326</v>
+      </c>
+      <c r="C21">
+        <v>2287.9429205479451</v>
+      </c>
+      <c r="D21">
+        <f>AVERAGE(B6:B24)</f>
+        <v>188</v>
+      </c>
+      <c r="E21">
+        <f>AVERAGE(C6:C24)</f>
+        <v>1656.1655090410957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>1975</v>
+      </c>
+      <c r="B22">
+        <v>157</v>
+      </c>
+      <c r="C22">
+        <v>1006.4054876712324</v>
+      </c>
+      <c r="D22">
+        <f>AVERAGE(B20:B25)</f>
+        <v>186.2</v>
+      </c>
+      <c r="E22">
+        <f>AVERAGE(C20:C25)</f>
+        <v>1510.6220635616437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>1977</v>
+      </c>
+      <c r="B24">
+        <v>61</v>
+      </c>
+      <c r="C24">
+        <v>711.22769863013707</v>
+      </c>
+      <c r="D24">
+        <f>AVERAGE(B21:B26)</f>
+        <v>153.80000000000001</v>
+      </c>
+      <c r="E24">
+        <f>AVERAGE(C21:C26)</f>
+        <v>1207.6503063013695</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>1978</v>
+      </c>
+      <c r="B25">
+        <v>182</v>
+      </c>
+      <c r="C25">
+        <v>1407.1111835616432</v>
+      </c>
+      <c r="D25">
+        <f>AVERAGE(B22:B27)</f>
+        <v>90</v>
+      </c>
+      <c r="E25">
+        <f>AVERAGE(C22:C27)</f>
+        <v>818.86477519724508</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1979</v>
+      </c>
+      <c r="B26">
+        <v>43</v>
+      </c>
+      <c r="C26">
+        <v>625.56424109589022</v>
+      </c>
+      <c r="D26">
+        <f t="shared" ref="D26:D62" si="0">AVERAGE(B24:B28)</f>
+        <v>62.6</v>
+      </c>
+      <c r="E26">
+        <f t="shared" ref="E26:E63" si="1">AVERAGE(C24:C28)</f>
+        <v>666.04050423834099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
         <v>1980</v>
       </c>
-      <c r="B12">
+      <c r="B27">
         <v>7</v>
       </c>
-      <c r="C12">
+      <c r="C27">
         <v>344.0152650273223</v>
       </c>
-      <c r="D12">
+      <c r="D27">
         <f t="shared" si="0"/>
         <v>51.6</v>
       </c>
-      <c r="E12">
+      <c r="E27">
         <f t="shared" si="1"/>
         <v>563.76108999176563</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>1981</v>
       </c>
-      <c r="B13">
+      <c r="B28">
         <v>20</v>
       </c>
-      <c r="C13">
+      <c r="C28">
         <v>242.28413287671208</v>
       </c>
-      <c r="D13">
+      <c r="D28">
         <f t="shared" si="0"/>
         <v>23.6</v>
       </c>
-      <c r="E13">
+      <c r="E28">
         <f t="shared" si="1"/>
         <v>364.85345985477949</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
         <v>1982</v>
       </c>
-      <c r="B14">
+      <c r="B29">
         <v>6</v>
       </c>
-      <c r="C14">
+      <c r="C29">
         <v>199.8306273972604</v>
       </c>
-      <c r="D14">
+      <c r="D29">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E14">
+      <c r="E29">
         <f t="shared" si="1"/>
         <v>421.3065362257654</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
         <v>1983</v>
       </c>
-      <c r="B15">
+      <c r="B30">
         <v>42</v>
       </c>
-      <c r="C15">
+      <c r="C30">
         <v>412.57303287671243</v>
       </c>
-      <c r="D15">
+      <c r="D30">
         <f t="shared" si="0"/>
         <v>52.8</v>
       </c>
-      <c r="E15">
+      <c r="E30">
         <f t="shared" si="1"/>
         <v>462.68750623399956</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
         <v>1984</v>
       </c>
-      <c r="B16">
+      <c r="B31">
         <v>130</v>
       </c>
-      <c r="C16">
+      <c r="C31">
         <v>907.82962295081984</v>
       </c>
-      <c r="D16">
+      <c r="D31">
         <f t="shared" si="0"/>
         <v>71.2</v>
       </c>
-      <c r="E16">
+      <c r="E31">
         <f t="shared" si="1"/>
         <v>562.54211637098581</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
         <v>1985</v>
       </c>
-      <c r="B17">
+      <c r="B32">
         <v>66</v>
       </c>
-      <c r="C17">
+      <c r="C32">
         <v>550.92011506849303</v>
       </c>
-      <c r="D17">
+      <c r="D32">
         <f t="shared" si="0"/>
         <v>79.599999999999994</v>
       </c>
-      <c r="E17">
+      <c r="E32">
         <f t="shared" si="1"/>
         <v>623.26802212441066</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
         <v>1986</v>
       </c>
-      <c r="B18">
+      <c r="B33">
         <v>112</v>
       </c>
-      <c r="C18">
+      <c r="C33">
         <v>741.55718356164346</v>
       </c>
-      <c r="D18">
+      <c r="D33">
         <f t="shared" si="0"/>
         <v>84.8</v>
       </c>
-      <c r="E18">
+      <c r="E33">
         <f t="shared" si="1"/>
         <v>663.14899970207375</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
         <v>1987</v>
       </c>
-      <c r="B19">
+      <c r="B34">
         <v>48</v>
       </c>
-      <c r="C19">
+      <c r="C34">
         <v>503.46015616438433</v>
       </c>
-      <c r="D19">
+      <c r="D34">
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="E19">
+      <c r="E34">
         <f t="shared" si="1"/>
         <v>775.9497310023205</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
         <v>1988</v>
       </c>
-      <c r="B20">
+      <c r="B35">
         <v>68</v>
       </c>
-      <c r="C20">
+      <c r="C35">
         <v>611.97792076502799</v>
       </c>
-      <c r="D20">
+      <c r="D35">
         <f t="shared" si="0"/>
         <v>135.6</v>
       </c>
-      <c r="E20">
+      <c r="E35">
         <f t="shared" si="1"/>
         <v>1014.2061096324572</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
         <v>1989</v>
       </c>
-      <c r="B21">
+      <c r="B36">
         <v>201</v>
       </c>
-      <c r="C21">
+      <c r="C36">
         <v>1471.8332794520538</v>
       </c>
-      <c r="D21">
+      <c r="D36">
         <f t="shared" si="0"/>
         <v>123.8</v>
       </c>
-      <c r="E21">
+      <c r="E36">
         <f t="shared" si="1"/>
         <v>953.36990086533388</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
         <v>1990</v>
       </c>
-      <c r="B22">
+      <c r="B37">
         <v>249</v>
       </c>
-      <c r="C22">
+      <c r="C37">
         <v>1742.2020082191766</v>
       </c>
-      <c r="D22">
+      <c r="D37">
         <f t="shared" si="0"/>
         <v>124</v>
       </c>
-      <c r="E22">
+      <c r="E37">
         <f t="shared" si="1"/>
         <v>929.4437849330036</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
         <v>1991</v>
       </c>
-      <c r="B23">
+      <c r="B38">
         <v>53</v>
       </c>
-      <c r="C23">
+      <c r="C38">
         <v>437.37613972602685</v>
       </c>
-      <c r="D23">
+      <c r="D38">
         <f t="shared" si="0"/>
         <v>140</v>
       </c>
-      <c r="E23">
+      <c r="E38">
         <f t="shared" si="1"/>
         <v>971.64087091698423</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
         <v>1992</v>
       </c>
-      <c r="B24">
+      <c r="B39">
         <v>49</v>
       </c>
-      <c r="C24">
+      <c r="C39">
         <v>383.82957650273198</v>
       </c>
-      <c r="D24">
+      <c r="D39">
         <f t="shared" si="0"/>
         <v>104.2</v>
       </c>
-      <c r="E24">
+      <c r="E39">
         <f t="shared" si="1"/>
         <v>713.20487091698431</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
         <v>1993</v>
       </c>
-      <c r="B25">
+      <c r="B40">
         <v>148</v>
       </c>
-      <c r="C25">
+      <c r="C40">
         <v>822.96335068493136</v>
       </c>
-      <c r="D25">
+      <c r="D40">
         <f t="shared" si="0"/>
         <v>58.4</v>
       </c>
-      <c r="E25">
+      <c r="E40">
         <f t="shared" si="1"/>
         <v>405.32424516355991</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
         <v>1994</v>
       </c>
-      <c r="B26">
+      <c r="B41">
         <v>22</v>
       </c>
-      <c r="C26">
+      <c r="C41">
         <v>179.65327945205485</v>
       </c>
-      <c r="D26">
+      <c r="D41">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="E26">
+      <c r="E41">
         <f t="shared" si="1"/>
         <v>439.22432705442014</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
         <v>1995</v>
       </c>
-      <c r="B27">
+      <c r="B42">
         <v>20</v>
       </c>
-      <c r="C27">
+      <c r="C42">
         <v>202.79887945205451</v>
       </c>
-      <c r="D27">
+      <c r="D42">
         <f t="shared" si="0"/>
         <v>60.8</v>
       </c>
-      <c r="E27">
+      <c r="E42">
         <f t="shared" si="1"/>
         <v>407.67692463058609</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
         <v>1996</v>
       </c>
-      <c r="B28">
+      <c r="B43">
         <v>96</v>
       </c>
-      <c r="C28">
+      <c r="C43">
         <v>606.87654918032797</v>
       </c>
-      <c r="D28">
+      <c r="D43">
         <f t="shared" si="0"/>
         <v>65.2</v>
       </c>
-      <c r="E28">
+      <c r="E43">
         <f t="shared" si="1"/>
         <v>436.60425832921629</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
         <v>1997</v>
       </c>
-      <c r="B29">
+      <c r="B44">
         <v>18</v>
       </c>
-      <c r="C29">
+      <c r="C44">
         <v>226.09256438356167</v>
       </c>
-      <c r="D29">
+      <c r="D44">
         <f t="shared" si="0"/>
         <v>84.6</v>
       </c>
-      <c r="E29">
+      <c r="E44">
         <f t="shared" si="1"/>
         <v>541.43964408264105</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
         <v>1998</v>
       </c>
-      <c r="B30">
+      <c r="B45">
         <v>170</v>
       </c>
-      <c r="C30">
+      <c r="C45">
         <v>967.60001917808245</v>
       </c>
-      <c r="D30">
+      <c r="D45">
         <f t="shared" si="0"/>
         <v>139.6</v>
       </c>
-      <c r="E30">
+      <c r="E45">
         <f t="shared" si="1"/>
         <v>810.79264742720284</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
         <v>1999</v>
       </c>
-      <c r="B31">
+      <c r="B46">
         <v>119</v>
       </c>
-      <c r="C31">
+      <c r="C46">
         <v>703.83020821917842</v>
       </c>
-      <c r="D31">
+      <c r="D46">
         <f t="shared" si="0"/>
         <v>132.19999999999999</v>
       </c>
-      <c r="E31">
+      <c r="E46">
         <f t="shared" si="1"/>
         <v>800.77531676921922</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
         <v>2000</v>
       </c>
-      <c r="B32">
+      <c r="B47">
         <v>295</v>
       </c>
-      <c r="C32">
+      <c r="C47">
         <v>1549.5638961748632</v>
       </c>
-      <c r="D32">
+      <c r="D47">
         <f t="shared" si="0"/>
         <v>134</v>
       </c>
-      <c r="E32">
+      <c r="E47">
         <f t="shared" si="1"/>
         <v>799.5123271801782</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
         <v>2001</v>
       </c>
-      <c r="B33">
+      <c r="B48">
         <v>59</v>
       </c>
-      <c r="C33">
+      <c r="C48">
         <v>556.78989589041066</v>
       </c>
-      <c r="D33">
+      <c r="D48">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="E33">
+      <c r="E48">
         <f t="shared" si="1"/>
         <v>626.81244827606849</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
         <v>2002</v>
       </c>
-      <c r="B34">
+      <c r="B49">
         <v>27</v>
       </c>
-      <c r="C34">
+      <c r="C49">
         <v>219.77761643835618</v>
       </c>
-      <c r="D34">
+      <c r="D49">
         <f t="shared" si="0"/>
         <v>76.2</v>
       </c>
-      <c r="E34">
+      <c r="E49">
         <f t="shared" si="1"/>
         <v>495.05426783441862</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
         <v>2003</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
         <v>104.10062465753411</v>
       </c>
-      <c r="D35">
+      <c r="D50">
         <f t="shared" si="0"/>
         <v>26.8</v>
       </c>
-      <c r="E35">
+      <c r="E50">
         <f t="shared" si="1"/>
         <v>222.06458284602132</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
         <v>2004</v>
       </c>
-      <c r="B36">
-        <v>0</v>
-      </c>
-      <c r="C36">
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
         <v>45.039306010928961</v>
       </c>
-      <c r="D36">
+      <c r="D51">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E36">
+      <c r="E51">
         <f t="shared" si="1"/>
         <v>122.96708585971999</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
         <v>2005</v>
       </c>
-      <c r="B37">
+      <c r="B52">
         <v>48</v>
       </c>
-      <c r="C37">
+      <c r="C52">
         <v>184.61547123287667</v>
       </c>
-      <c r="D37">
-        <f t="shared" si="0"/>
+      <c r="D52">
+        <f>AVERAGE(B50:B55)</f>
         <v>10.4</v>
       </c>
-      <c r="E37">
-        <f t="shared" si="1"/>
+      <c r="E52">
+        <f>AVERAGE(C50:C55)</f>
         <v>92.439715850737286</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
         <v>2006</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-      <c r="C38">
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
         <v>61.302410958904062</v>
       </c>
-      <c r="D38">
-        <f t="shared" si="0"/>
+      <c r="D53">
+        <f>AVERAGE(B51:B57)</f>
         <v>43.4</v>
       </c>
-      <c r="E38">
-        <f t="shared" si="1"/>
+      <c r="E53">
+        <f>AVERAGE(C51:C57)</f>
         <v>245.53169174114828</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
         <v>2008</v>
       </c>
-      <c r="B39">
+      <c r="B55">
         <v>4</v>
       </c>
-      <c r="C39">
+      <c r="C55">
         <v>67.140766393442661</v>
       </c>
-      <c r="D39">
-        <f t="shared" si="0"/>
+      <c r="D55">
+        <f>AVERAGE(B52:B58)</f>
         <v>69.2</v>
       </c>
-      <c r="E39">
-        <f t="shared" si="1"/>
+      <c r="E55">
+        <f>AVERAGE(C52:C58)</f>
         <v>402.27257848416792</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
         <v>2010</v>
       </c>
-      <c r="B40">
+      <c r="B57">
         <v>165</v>
       </c>
-      <c r="C40">
+      <c r="C57">
         <v>869.56050410958892</v>
       </c>
-      <c r="D40">
-        <f t="shared" si="0"/>
+      <c r="D57">
+        <f>AVERAGE(B53:B59)</f>
         <v>110.6</v>
       </c>
-      <c r="E40">
-        <f t="shared" si="1"/>
+      <c r="E57">
+        <f>AVERAGE(C53:C59)</f>
         <v>635.50607002994218</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
         <v>2011</v>
       </c>
-      <c r="B41">
+      <c r="B58">
         <v>129</v>
       </c>
-      <c r="C41">
+      <c r="C58">
         <v>828.74373972602746</v>
       </c>
-      <c r="D41">
-        <f t="shared" si="0"/>
+      <c r="D58">
+        <f>AVERAGE(B55:B60)</f>
         <v>114.6</v>
       </c>
-      <c r="E41">
-        <f t="shared" si="1"/>
+      <c r="E58">
+        <f>AVERAGE(C55:C60)</f>
         <v>683.47151989295594</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>2012</v>
       </c>
-      <c r="B42">
+      <c r="B59">
         <v>255</v>
       </c>
-      <c r="C42">
+      <c r="C59">
         <v>1350.782928961748</v>
       </c>
-      <c r="D42">
+      <c r="D59">
         <f t="shared" si="0"/>
         <v>113.8</v>
       </c>
-      <c r="E42">
+      <c r="E59">
         <f t="shared" si="1"/>
         <v>700.30691510741804</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>2013</v>
       </c>
-      <c r="B43">
+      <c r="B60">
         <v>20</v>
       </c>
-      <c r="C43">
+      <c r="C60">
         <v>301.12966027397277</v>
       </c>
-      <c r="D43">
+      <c r="D60">
         <f t="shared" si="0"/>
         <v>80.8</v>
       </c>
-      <c r="E43">
+      <c r="E60">
         <f t="shared" si="1"/>
         <v>556.7041025046783</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
         <v>2014</v>
       </c>
-      <c r="B44">
-        <v>0</v>
-      </c>
-      <c r="C44">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
         <v>151.31774246575344</v>
       </c>
-      <c r="D44">
+      <c r="D61">
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="E44">
+      <c r="E61">
         <f t="shared" si="1"/>
         <v>597.68890319335276</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
         <v>2015</v>
       </c>
-      <c r="B45">
-        <v>0</v>
-      </c>
-      <c r="C45">
+      <c r="B62">
+        <v>0</v>
+      </c>
+      <c r="C62">
         <v>151.5464410958904</v>
       </c>
-      <c r="D45">
+      <c r="D62">
         <f t="shared" si="0"/>
         <v>60.6</v>
       </c>
-      <c r="E45">
+      <c r="E62">
         <f t="shared" si="1"/>
         <v>442.60197383935946</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63">
         <v>2016</v>
       </c>
-      <c r="B46">
+      <c r="B63">
         <v>190</v>
       </c>
-      <c r="C46">
+      <c r="C63">
         <v>1033.667743169399</v>
       </c>
-      <c r="D46">
-        <f>AVERAGE(B44:B48)</f>
+      <c r="D63">
+        <f>AVERAGE(B61:B65)</f>
         <v>60.2</v>
       </c>
-      <c r="E46">
+      <c r="E63">
         <f t="shared" si="1"/>
         <v>432.85270534620867</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64">
         <v>2017</v>
       </c>
-      <c r="B47">
+      <c r="B64">
         <v>93</v>
       </c>
-      <c r="C47">
+      <c r="C64">
         <v>575.34828219178155</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A65">
         <v>2018</v>
       </c>
-      <c r="B48">
+      <c r="B65">
         <v>18</v>
       </c>
-      <c r="C48">
+      <c r="C65">
         <v>252.38331780821912</v>
       </c>
     </row>
@@ -11839,7 +12747,7 @@
         <v>34460.833333333336</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>1965</v>
       </c>
@@ -11847,7 +12755,7 @@
         <v>19589.166666666668</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>1966</v>
       </c>
@@ -11855,7 +12763,7 @@
         <v>11349.166666666666</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>1967</v>
       </c>
@@ -11863,7 +12771,7 @@
         <v>8334.1666666666661</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>1968</v>
       </c>
@@ -11871,7 +12779,7 @@
         <v>12847.5</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>1969</v>
       </c>
@@ -11879,7 +12787,7 @@
         <v>19190.833333333332</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>1970</v>
       </c>
@@ -11887,7 +12795,7 @@
         <v>26112.5</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>1971</v>
       </c>
@@ -11895,7 +12803,7 @@
         <v>31705.833333333332</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>1972</v>
       </c>
@@ -11903,7 +12811,7 @@
         <v>11945</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>1973</v>
       </c>
@@ -11911,7 +12819,7 @@
         <v>44006.666666666664</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>1974</v>
       </c>
@@ -11919,9 +12827,8 @@
         <v>101742.5</v>
       </c>
       <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>1975</v>
       </c>
@@ -11931,9 +12838,8 @@
       <c r="C75">
         <v>60226.666666666664</v>
       </c>
-      <c r="E75" s="1"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>1976</v>
       </c>
@@ -11943,9 +12849,8 @@
       <c r="C76">
         <v>52407.5</v>
       </c>
-      <c r="E76" s="1"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>1977</v>
       </c>
@@ -11955,9 +12860,8 @@
       <c r="C77">
         <v>15504.109075670496</v>
       </c>
-      <c r="E77" s="1"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>1978</v>
       </c>
@@ -11967,9 +12871,8 @@
       <c r="C78">
         <v>22053.857439335887</v>
       </c>
-      <c r="E78" s="1"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>1979</v>
       </c>
@@ -11979,9 +12882,8 @@
       <c r="C79">
         <v>12347.930395913156</v>
       </c>
-      <c r="E79" s="1"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>1980</v>
       </c>
@@ -11991,9 +12893,8 @@
       <c r="C80">
         <v>6086.9932608100717</v>
       </c>
-      <c r="E80" s="1"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>1981</v>
       </c>
@@ -12001,9 +12902,8 @@
       <c r="C81">
         <v>25345.910068114095</v>
       </c>
-      <c r="E81" s="1"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>1982</v>
       </c>
@@ -12013,9 +12913,8 @@
       <c r="C82">
         <v>5092.5814176245203</v>
       </c>
-      <c r="E82" s="1"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>1983</v>
       </c>
@@ -12023,9 +12922,8 @@
       <c r="C83">
         <v>22127.777526911144</v>
       </c>
-      <c r="E83" s="1"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>1984</v>
       </c>
@@ -12035,9 +12933,8 @@
       <c r="C84">
         <v>27153.613916256159</v>
       </c>
-      <c r="E84" s="1"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>1985</v>
       </c>
@@ -12045,9 +12942,8 @@
       <c r="C85">
         <v>6804.9681247339286</v>
       </c>
-      <c r="E85" s="1"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>1986</v>
       </c>
@@ -12055,9 +12951,8 @@
       <c r="C86">
         <v>17688.71980320381</v>
       </c>
-      <c r="E86" s="1"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>1987</v>
       </c>
@@ -12065,9 +12960,8 @@
       <c r="C87">
         <v>9862.2378139633893</v>
       </c>
-      <c r="E87" s="1"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>1988</v>
       </c>
@@ -12077,9 +12971,8 @@
       <c r="C88">
         <v>16285.588553639847</v>
       </c>
-      <c r="E88" s="1"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>1989</v>
       </c>
@@ -12089,9 +12982,8 @@
       <c r="C89">
         <v>39978.924467395933</v>
       </c>
-      <c r="E89" s="1"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>1990</v>
       </c>
@@ -12099,9 +12991,8 @@
       <c r="C90">
         <v>38986.628104430689</v>
       </c>
-      <c r="E90" s="1"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>1991</v>
       </c>
@@ -12111,9 +13002,8 @@
       <c r="C91">
         <v>15310.266389953171</v>
       </c>
-      <c r="E91" s="1"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>1992</v>
       </c>
@@ -12123,9 +13013,8 @@
       <c r="C92">
         <v>23470.069387604733</v>
       </c>
-      <c r="E92" s="1"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>1993</v>
       </c>
@@ -12135,9 +13024,8 @@
       <c r="C93">
         <v>43983.723659986252</v>
       </c>
-      <c r="E93" s="1"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>1994</v>
       </c>
@@ -12147,9 +13035,8 @@
       <c r="C94">
         <v>9164.3634418901656</v>
       </c>
-      <c r="E94" s="1"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>1995</v>
       </c>
@@ -12159,9 +13046,8 @@
       <c r="C95">
         <v>15897.976692209451</v>
       </c>
-      <c r="E95" s="1"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>1996</v>
       </c>
@@ -12169,9 +13055,8 @@
       <c r="C96">
         <v>27928.722790093045</v>
       </c>
-      <c r="E96" s="1"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>1997</v>
       </c>
@@ -12181,9 +13066,8 @@
       <c r="C97">
         <v>7659.5715091528318</v>
       </c>
-      <c r="E97" s="1"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>1998</v>
       </c>
@@ -12193,9 +13077,8 @@
       <c r="C98">
         <v>10759.175830140484</v>
       </c>
-      <c r="E98" s="1"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>1999</v>
       </c>
@@ -12203,9 +13086,8 @@
       <c r="C99">
         <v>9256.6602117922503</v>
       </c>
-      <c r="E99" s="1"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>2000</v>
       </c>
@@ -12213,9 +13095,8 @@
       <c r="C100">
         <v>15655.174753694582</v>
       </c>
-      <c r="E100" s="1"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>2001</v>
       </c>
@@ -12225,9 +13106,8 @@
       <c r="C101">
         <v>9186.9554590099124</v>
       </c>
-      <c r="E101" s="1"/>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>2002</v>
       </c>
@@ -12237,9 +13117,8 @@
       <c r="C102">
         <v>5102.9829821200528</v>
       </c>
-      <c r="E102" s="1"/>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>2003</v>
       </c>
@@ -12249,9 +13128,8 @@
       <c r="C103">
         <v>5584.2487760749254</v>
       </c>
-      <c r="E103" s="1"/>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>2004</v>
       </c>
@@ -12261,9 +13139,8 @@
       <c r="C104">
         <v>5151.0735974274767</v>
       </c>
-      <c r="E104" s="1"/>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>2005</v>
       </c>
@@ -12273,9 +13150,8 @@
       <c r="C105">
         <v>6372.3257343550458</v>
       </c>
-      <c r="E105" s="1"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>2006</v>
       </c>
@@ -12285,9 +13161,8 @@
       <c r="C106">
         <v>4830.9964772243511</v>
       </c>
-      <c r="E106" s="1"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>2007</v>
       </c>
@@ -12297,9 +13172,8 @@
       <c r="C107">
         <v>2819.1602577499129</v>
       </c>
-      <c r="E107" s="1"/>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>2008</v>
       </c>
@@ -12309,9 +13183,8 @@
       <c r="C108">
         <v>3021.3578680897649</v>
       </c>
-      <c r="E108" s="1"/>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>2009</v>
       </c>
@@ -12321,9 +13194,8 @@
       <c r="C109">
         <v>3213.6281800766287</v>
       </c>
-      <c r="E109" s="1"/>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>2010</v>
       </c>
@@ -12333,9 +13205,8 @@
       <c r="C110">
         <v>16677.079514687099</v>
       </c>
-      <c r="E110" s="1"/>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>2011</v>
       </c>
@@ -12345,9 +13216,8 @@
       <c r="C111">
         <v>39678.263122605371</v>
       </c>
-      <c r="E111" s="1"/>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>2012</v>
       </c>
@@ -12357,9 +13227,8 @@
       <c r="C112">
         <v>32015.053178708262</v>
       </c>
-      <c r="E112" s="1"/>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>2013</v>
       </c>
@@ -12369,9 +13238,8 @@
       <c r="C113">
         <v>10514.634578544061</v>
       </c>
-      <c r="E113" s="1"/>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>2014</v>
       </c>
@@ -12381,9 +13249,8 @@
       <c r="C114">
         <v>7492.3128033205612</v>
       </c>
-      <c r="E114" s="1"/>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>2015</v>
       </c>
@@ -12393,9 +13260,8 @@
       <c r="C115">
         <v>7306.0630161770969</v>
       </c>
-      <c r="E115" s="1"/>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>2016</v>
       </c>
@@ -12405,9 +13271,8 @@
       <c r="C116">
         <v>23787.066085112208</v>
       </c>
-      <c r="E116" s="1"/>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>2017</v>
       </c>
@@ -12417,9 +13282,8 @@
       <c r="C117">
         <v>8720.5904108131126</v>
       </c>
-      <c r="E117" s="1"/>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>2018</v>
       </c>
@@ -12429,9 +13293,8 @@
       <c r="C118">
         <v>6437.8788207747975</v>
       </c>
-      <c r="E118" s="1"/>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>2019</v>
       </c>
@@ -12441,9 +13304,8 @@
       <c r="C119">
         <v>7013.3574393358876</v>
       </c>
-      <c r="E119" s="1"/>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>2020</v>
       </c>
@@ -12453,7 +13315,6 @@
       <c r="C120">
         <v>8074.0108784893273</v>
       </c>
-      <c r="E120" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12462,24 +13323,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C27CB6A7-D73D-45E8-A823-7ECEBBE940B5}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1994</v>
       </c>
@@ -12487,303 +13345,262 @@
         <v>31</v>
       </c>
       <c r="C2">
+        <v>456.41235890410985</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>1996</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>185.19059289617485</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>1998</v>
+      </c>
+      <c r="B6">
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>256.52723287671307</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>2002</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>36.999027397260278</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2003</v>
+      </c>
+      <c r="B11">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>229.49576164383552</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>2004</v>
+      </c>
+      <c r="B12">
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>367.69956284153005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>2005</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+      <c r="C13">
+        <v>49.123800000000024</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>2006</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>5.5807534246575363</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2007</v>
+      </c>
+      <c r="B15">
+        <v>41</v>
+      </c>
+      <c r="C15">
+        <v>813.37021369862987</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2008</v>
+      </c>
+      <c r="B16">
+        <v>42</v>
+      </c>
+      <c r="C16">
+        <v>1240.8468825136615</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>2009</v>
+      </c>
+      <c r="B17">
         <v>3</v>
       </c>
-      <c r="D2">
-        <v>456.41235890410985</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>1996</v>
-      </c>
-      <c r="B3">
+      <c r="C17">
+        <v>41.404868493150687</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>2010</v>
+      </c>
+      <c r="B18">
+        <v>117</v>
+      </c>
+      <c r="C18">
+        <v>2837.4747178082184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>2011</v>
+      </c>
+      <c r="B19">
+        <v>44</v>
+      </c>
+      <c r="C19">
+        <v>688.51548493150676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>2012</v>
+      </c>
+      <c r="B20">
+        <v>40</v>
+      </c>
+      <c r="C20">
+        <v>1579.5266748633874</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2013</v>
+      </c>
+      <c r="B21">
+        <v>0</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>2014</v>
+      </c>
+      <c r="B22">
+        <v>0</v>
+      </c>
+      <c r="C22">
+        <v>6.7521917808219181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>2015</v>
+      </c>
+      <c r="B23">
+        <v>5</v>
+      </c>
+      <c r="C23">
+        <v>50.225054794520538</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>2016</v>
+      </c>
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24">
+        <v>347.9419480874318</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>2017</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>1.3491479452054798</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2018</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26">
+        <v>29.783536986301364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>2019</v>
+      </c>
+      <c r="B27">
         <v>11</v>
       </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>185.19059289617485</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>1998</v>
-      </c>
-      <c r="B4">
-        <v>21</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>256.52723287671307</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2002</v>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>36.999027397260278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>2003</v>
-      </c>
-      <c r="B6">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>229.49576164383552</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>2004</v>
-      </c>
-      <c r="B7">
-        <v>27</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>367.69956284153005</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>2005</v>
-      </c>
-      <c r="B8">
-        <v>5</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>49.123800000000024</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>2006</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>5.5807534246575363</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>2007</v>
-      </c>
-      <c r="B10">
-        <v>41</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>813.37021369862987</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>2008</v>
-      </c>
-      <c r="B11">
-        <v>42</v>
-      </c>
-      <c r="C11">
-        <v>8</v>
-      </c>
-      <c r="D11">
-        <v>1240.8468825136615</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>2009</v>
-      </c>
-      <c r="B12">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>41.404868493150687</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>2010</v>
-      </c>
-      <c r="B13">
-        <v>117</v>
-      </c>
-      <c r="C13">
-        <v>13</v>
-      </c>
-      <c r="D13">
-        <v>2837.4747178082184</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>2011</v>
-      </c>
-      <c r="B14">
-        <v>44</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>688.51548493150676</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>2012</v>
-      </c>
-      <c r="B15">
-        <v>40</v>
-      </c>
-      <c r="C15">
-        <v>10</v>
-      </c>
-      <c r="D15">
-        <v>1579.5266748633874</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>2013</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>2014</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17">
-        <v>6.7521917808219181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>2015</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
-      </c>
-      <c r="D18">
-        <v>50.225054794520538</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>2016</v>
-      </c>
-      <c r="B19">
-        <v>21</v>
-      </c>
-      <c r="C19">
-        <v>0</v>
-      </c>
-      <c r="D19">
-        <v>347.9419480874318</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>2017</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
-        <v>1.3491479452054798</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>2018</v>
-      </c>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
-        <v>29.783536986301364</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>2019</v>
-      </c>
-      <c r="B22">
-        <v>11</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
+      <c r="C27">
         <v>285.26690136986309</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28">
         <v>2020</v>
       </c>
-      <c r="B23">
+      <c r="B28">
         <v>22</v>
       </c>
-      <c r="C23">
-        <v>11</v>
-      </c>
-      <c r="D23">
+      <c r="C28">
         <v>1152.0254316939888</v>
       </c>
     </row>
